--- a/docs/exports/enum.xlsx
+++ b/docs/exports/enum.xlsx
@@ -14,7 +14,7 @@
     <sheet name="土地の用途地域 (LandUseZone)" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="連絡先の種類 (ContactPointType)" sheetId="7" state="visible" r:id="rId7"/>
     <sheet name="制御対象 (ControlledProperty)" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="ID種別 (IdentificatonType)" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="ID種別 (IdentificationType)" sheetId="9" state="visible" r:id="rId9"/>
     <sheet name="施設の部位 (BuildingComponent)" sheetId="10" state="visible" r:id="rId10"/>
     <sheet name="不具合原因 (Cause)" sheetId="11" state="visible" r:id="rId11"/>
     <sheet name="簡易処置 (DamageControl)" sheetId="12" state="visible" r:id="rId12"/>
@@ -724,7 +724,7 @@
       <c r="A9" s="3" t="inlineStr">
         <is>
           <t>ID種別
-(IdentificatonType)</t>
+(IdentificationType)</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
@@ -739,7 +739,7 @@
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>https://ppp-database.org/spec/enum/IdentificatonType/</t>
+          <t>https://ppp-database.org/spec/enum/IdentificationType/</t>
         </is>
       </c>
     </row>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="L13" s="0" t="inlineStr">
         <is>
-          <t>コンペア</t>
+          <t>コンベア</t>
         </is>
       </c>
       <c r="M13" s="0" t="inlineStr">
@@ -1588,7 +1588,7 @@
       </c>
       <c r="L14" s="0" t="inlineStr">
         <is>
-          <t>コンペア</t>
+          <t>コンベア</t>
         </is>
       </c>
       <c r="M14" s="0" t="inlineStr">
@@ -1630,7 +1630,7 @@
       </c>
       <c r="L15" s="0" t="inlineStr">
         <is>
-          <t>コンペア</t>
+          <t>コンベア</t>
         </is>
       </c>
       <c r="M15" s="0" t="inlineStr">
@@ -1672,7 +1672,7 @@
       </c>
       <c r="L16" s="0" t="inlineStr">
         <is>
-          <t>コンペア</t>
+          <t>コンベア</t>
         </is>
       </c>
       <c r="M16" s="0" t="inlineStr">
@@ -1714,7 +1714,7 @@
       </c>
       <c r="L17" s="0" t="inlineStr">
         <is>
-          <t>コンペア</t>
+          <t>コンベア</t>
         </is>
       </c>
       <c r="M17" s="0" t="inlineStr">
@@ -3979,7 +3979,7 @@
       </c>
       <c r="J92" s="0" t="inlineStr">
         <is>
-          <t>コンペア</t>
+          <t>コンベア</t>
         </is>
       </c>
       <c r="L92" s="0" t="inlineStr">

--- a/docs/exports/enum.xlsx
+++ b/docs/exports/enum.xlsx
@@ -956,7 +956,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:M142"/>
+  <dimension ref="A1:M155"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="12"/>
   <cols>
     <col width="14.140625" bestFit="1" customWidth="1" style="9" min="1" max="1"/>
@@ -975,3932 +975,4381 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="8" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>カテゴリ</t>
         </is>
       </c>
-      <c r="C1" s="8" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>サブカテゴリ</t>
         </is>
       </c>
-      <c r="F1" s="8" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>用語(建物)</t>
         </is>
       </c>
-      <c r="I1" s="8" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>用語(設備)</t>
         </is>
       </c>
-      <c r="L1" s="8" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>用語(設備)</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="C2" s="8" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>カテゴリ</t>
         </is>
       </c>
-      <c r="D2" s="8" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>サブカテゴリ</t>
         </is>
       </c>
-      <c r="F2" s="8" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>サブカテゴリ</t>
         </is>
       </c>
-      <c r="G2" s="8" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>用語(分類用語)</t>
         </is>
       </c>
-      <c r="I2" s="8" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>サブカテゴリ</t>
         </is>
       </c>
-      <c r="J2" s="8" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>用語(分類用語)</t>
         </is>
       </c>
-      <c r="L2" s="8" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>分類用語</t>
         </is>
       </c>
-      <c r="M2" s="8" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>用語</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="0" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>建物の部位</t>
         </is>
       </c>
-      <c r="C3" s="0" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>建物の部位</t>
         </is>
       </c>
-      <c r="D3" s="0" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>建築外部</t>
         </is>
       </c>
-      <c r="F3" s="0" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>建築外部</t>
         </is>
       </c>
-      <c r="G3" s="0" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>屋上</t>
         </is>
       </c>
-      <c r="I3" s="0" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>電灯・動力設備</t>
         </is>
       </c>
-      <c r="J3" s="0" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>外灯</t>
         </is>
       </c>
-      <c r="L3" s="0" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>湯沸器</t>
         </is>
       </c>
-      <c r="M3" s="0" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>貯蔵湯沸器</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="0" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>建物外の部位</t>
         </is>
       </c>
-      <c r="C4" s="0" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>建物の部位</t>
         </is>
       </c>
-      <c r="D4" s="0" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>建物内部</t>
         </is>
       </c>
-      <c r="F4" s="0" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>建築外部</t>
         </is>
       </c>
-      <c r="G4" s="0" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>屋根</t>
         </is>
       </c>
-      <c r="I4" s="0" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>電灯・動力設備</t>
         </is>
       </c>
-      <c r="J4" s="0" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>照明器具</t>
         </is>
       </c>
-      <c r="L4" s="0" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>湯沸器</t>
         </is>
       </c>
-      <c r="M4" s="0" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>瞬間湯沸器</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="0" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>電気設備</t>
         </is>
       </c>
-      <c r="C5" s="0" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>建物外の部位</t>
         </is>
       </c>
-      <c r="D5" s="0" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>建物外構</t>
         </is>
       </c>
-      <c r="F5" s="0" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>建築外部</t>
         </is>
       </c>
-      <c r="G5" s="0" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>外壁・擁壁</t>
         </is>
       </c>
-      <c r="I5" s="0" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>電灯・動力設備</t>
         </is>
       </c>
-      <c r="J5" s="0" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t>その他電灯設備</t>
         </is>
       </c>
-      <c r="L5" s="0" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>湯沸器</t>
         </is>
       </c>
-      <c r="M5" s="0" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>温水ボイラー・温水器</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="0" t="inlineStr">
+      <c r="A6" t="inlineStr">
         <is>
           <t>機械設備</t>
         </is>
       </c>
-      <c r="C6" s="0" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>電気設備</t>
         </is>
       </c>
-      <c r="D6" s="0" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>電灯・動力設備</t>
         </is>
       </c>
-      <c r="F6" s="0" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>建築外部</t>
         </is>
       </c>
-      <c r="G6" s="0" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>ひさし・玄関</t>
         </is>
       </c>
-      <c r="I6" s="0" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>電灯・動力設備</t>
         </is>
       </c>
-      <c r="J6" s="0" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t>制御機器</t>
         </is>
       </c>
-      <c r="L6" s="0" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>湯沸器</t>
         </is>
       </c>
-      <c r="M6" s="0" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>電気温水器</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="0" t="inlineStr">
+      <c r="A7" t="inlineStr">
         <is>
           <t>防災設備</t>
         </is>
       </c>
-      <c r="C7" s="0" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>電気設備</t>
         </is>
       </c>
-      <c r="D7" s="0" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>受変電設備</t>
         </is>
       </c>
-      <c r="F7" s="0" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>建築外部</t>
         </is>
       </c>
-      <c r="G7" s="0" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>軒天</t>
         </is>
       </c>
-      <c r="I7" s="0" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t>電灯・動力設備</t>
         </is>
       </c>
-      <c r="J7" s="0" t="inlineStr">
+      <c r="J7" t="inlineStr">
         <is>
           <t>その他動力設備</t>
         </is>
       </c>
-      <c r="L7" s="0" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>湯沸器</t>
         </is>
       </c>
-      <c r="M7" s="0" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>ブースター</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="0" t="inlineStr">
+      <c r="A8" t="inlineStr">
         <is>
           <t>搬送設備</t>
         </is>
       </c>
-      <c r="C8" s="0" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>電気設備</t>
         </is>
       </c>
-      <c r="D8" s="0" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>直流電源設備</t>
         </is>
       </c>
-      <c r="F8" s="0" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>建築外部</t>
         </is>
       </c>
-      <c r="G8" s="0" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>風除室</t>
         </is>
       </c>
-      <c r="I8" s="0" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t>電灯・動力設備</t>
         </is>
       </c>
-      <c r="J8" s="0" t="inlineStr">
+      <c r="J8" t="inlineStr">
         <is>
           <t>コンセント・スイッチ</t>
         </is>
       </c>
-      <c r="L8" s="0" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>湯沸器</t>
         </is>
       </c>
-      <c r="M8" s="0" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>温水循環ポンプ</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="0" t="inlineStr">
+      <c r="A9" t="inlineStr">
         <is>
           <t>厨房設備</t>
         </is>
       </c>
-      <c r="C9" s="0" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>電気設備</t>
         </is>
       </c>
-      <c r="D9" s="0" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>交流無停電電源設備</t>
         </is>
       </c>
-      <c r="F9" s="0" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>建築外部</t>
         </is>
       </c>
-      <c r="G9" s="0" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>フロントサッシ</t>
         </is>
       </c>
-      <c r="I9" s="0" t="inlineStr">
+      <c r="I9" t="inlineStr">
         <is>
           <t>電灯・動力設備</t>
         </is>
       </c>
-      <c r="J9" s="0" t="inlineStr">
+      <c r="J9" t="inlineStr">
         <is>
           <t>フォトセンサー</t>
         </is>
       </c>
-      <c r="L9" s="0" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>湯沸器</t>
         </is>
       </c>
-      <c r="M9" s="0" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>温水ボイラー</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="0" t="inlineStr">
+      <c r="A10" t="inlineStr">
         <is>
           <t>ガス設備</t>
         </is>
       </c>
-      <c r="C10" s="0" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>電気設備</t>
         </is>
       </c>
-      <c r="D10" s="0" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>太陽光発電設備</t>
         </is>
       </c>
-      <c r="F10" s="0" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>建築外部</t>
         </is>
       </c>
-      <c r="G10" s="0" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>自動ドア</t>
         </is>
       </c>
-      <c r="I10" s="0" t="inlineStr">
+      <c r="I10" t="inlineStr">
         <is>
           <t>電灯・動力設備</t>
         </is>
       </c>
-      <c r="J10" s="0" t="inlineStr">
+      <c r="J10" t="inlineStr">
         <is>
           <t>その他電気設備</t>
         </is>
       </c>
-      <c r="L10" s="0" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>湯沸器</t>
         </is>
       </c>
-      <c r="M10" s="0" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>貯湯槽</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="0" t="inlineStr">
+      <c r="A11" t="inlineStr">
         <is>
           <t>観測対象</t>
         </is>
       </c>
-      <c r="C11" s="0" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>電気設備</t>
         </is>
       </c>
-      <c r="D11" s="0" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>通信・情報設備</t>
         </is>
       </c>
-      <c r="F11" s="0" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>建築外部</t>
         </is>
       </c>
-      <c r="G11" s="0" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>入口ドア(手動)</t>
         </is>
       </c>
-      <c r="I11" s="0" t="inlineStr">
+      <c r="I11" t="inlineStr">
         <is>
           <t>受変電設備</t>
         </is>
       </c>
-      <c r="J11" s="0" t="inlineStr">
+      <c r="J11" t="inlineStr">
         <is>
           <t>メーターBOX</t>
         </is>
       </c>
-      <c r="L11" s="0" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t>湯沸器</t>
         </is>
       </c>
-      <c r="M11" s="0" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t>給湯用熱交換器</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">その他設備 </t>
-        </is>
-      </c>
-      <c r="C12" s="0" t="inlineStr">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>その他設備</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
         <is>
           <t>電気設備</t>
         </is>
       </c>
-      <c r="D12" s="0" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>防犯管理設備</t>
         </is>
       </c>
-      <c r="F12" s="0" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>建築外部</t>
         </is>
       </c>
-      <c r="G12" s="0" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>開き戸</t>
         </is>
       </c>
-      <c r="I12" s="0" t="inlineStr">
+      <c r="I12" t="inlineStr">
         <is>
           <t>受変電設備</t>
         </is>
       </c>
-      <c r="J12" s="0" t="inlineStr">
+      <c r="J12" t="inlineStr">
         <is>
           <t>キュービクル</t>
         </is>
       </c>
-      <c r="L12" s="0" t="inlineStr">
+      <c r="L12" t="inlineStr">
         <is>
           <t>湯沸器</t>
         </is>
       </c>
-      <c r="M12" s="0" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t>その他給湯器</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="C13" s="0" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>電気設備</t>
         </is>
       </c>
-      <c r="D13" s="0" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>雷保護設備</t>
         </is>
       </c>
-      <c r="F13" s="0" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>建築外部</t>
         </is>
       </c>
-      <c r="G13" s="0" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>引き戸・スライド扉</t>
         </is>
       </c>
-      <c r="I13" s="0" t="inlineStr">
+      <c r="I13" t="inlineStr">
         <is>
           <t>受変電設備</t>
         </is>
       </c>
-      <c r="J13" s="0" t="inlineStr">
+      <c r="J13" t="inlineStr">
         <is>
           <t>分電盤</t>
         </is>
       </c>
-      <c r="L13" s="0" t="inlineStr">
+      <c r="L13" t="inlineStr">
         <is>
           <t>コンベア</t>
         </is>
       </c>
-      <c r="M13" s="0" t="inlineStr">
+      <c r="M13" t="inlineStr">
         <is>
           <t>バケットコンベア</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="C14" s="0" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>電気設備</t>
         </is>
       </c>
-      <c r="D14" s="0" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>構内配電線路・通信線路設備</t>
         </is>
       </c>
-      <c r="F14" s="0" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>建築外部</t>
         </is>
       </c>
-      <c r="G14" s="0" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>窓</t>
         </is>
       </c>
-      <c r="I14" s="0" t="inlineStr">
+      <c r="I14" t="inlineStr">
         <is>
           <t>受変電設備</t>
         </is>
       </c>
-      <c r="J14" s="0" t="inlineStr">
+      <c r="J14" t="inlineStr">
         <is>
           <t>その他受変電設備</t>
         </is>
       </c>
-      <c r="L14" s="0" t="inlineStr">
+      <c r="L14" t="inlineStr">
         <is>
           <t>コンベア</t>
         </is>
       </c>
-      <c r="M14" s="0" t="inlineStr">
+      <c r="M14" t="inlineStr">
         <is>
           <t>スクリューコンベア</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="C15" s="0" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>機械設備</t>
         </is>
       </c>
-      <c r="D15" s="0" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>空気調和等設備</t>
         </is>
       </c>
-      <c r="F15" s="0" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t>建築外部</t>
         </is>
       </c>
-      <c r="G15" s="0" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t>トップライト</t>
         </is>
       </c>
-      <c r="I15" s="0" t="inlineStr">
+      <c r="I15" t="inlineStr">
         <is>
           <t>直流電源設備</t>
         </is>
       </c>
-      <c r="J15" s="0" t="inlineStr">
+      <c r="J15" t="inlineStr">
         <is>
           <t>バックアップ電源</t>
         </is>
       </c>
-      <c r="L15" s="0" t="inlineStr">
+      <c r="L15" t="inlineStr">
         <is>
           <t>コンベア</t>
         </is>
       </c>
-      <c r="M15" s="0" t="inlineStr">
+      <c r="M15" t="inlineStr">
         <is>
           <t>ローラーコンベア</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="C16" s="0" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>機械設備</t>
         </is>
       </c>
-      <c r="D16" s="0" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>給水機器</t>
         </is>
       </c>
-      <c r="F16" s="0" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>建築外部</t>
         </is>
       </c>
-      <c r="G16" s="0" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t>バルコニー</t>
         </is>
       </c>
-      <c r="I16" s="0" t="inlineStr">
+      <c r="I16" t="inlineStr">
         <is>
           <t>交流無停電電源設備</t>
         </is>
       </c>
-      <c r="J16" s="0" t="inlineStr">
+      <c r="J16" t="inlineStr">
         <is>
           <t>発電設備</t>
         </is>
       </c>
-      <c r="L16" s="0" t="inlineStr">
+      <c r="L16" t="inlineStr">
         <is>
           <t>コンベア</t>
         </is>
       </c>
-      <c r="M16" s="0" t="inlineStr">
+      <c r="M16" t="inlineStr">
         <is>
           <t>バーコンベア</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="C17" s="0" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>機械設備</t>
         </is>
       </c>
-      <c r="D17" s="0" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>排水機器</t>
         </is>
       </c>
-      <c r="F17" s="0" t="inlineStr">
+      <c r="F17" t="inlineStr">
         <is>
           <t>建築外部</t>
         </is>
       </c>
-      <c r="G17" s="0" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t>雨どい</t>
         </is>
       </c>
-      <c r="I17" s="0" t="inlineStr">
+      <c r="I17" t="inlineStr">
         <is>
           <t>太陽光発電設備</t>
         </is>
       </c>
-      <c r="J17" s="0" t="inlineStr">
+      <c r="J17" t="inlineStr">
         <is>
           <t>太陽光発電システム</t>
         </is>
       </c>
-      <c r="L17" s="0" t="inlineStr">
+      <c r="L17" t="inlineStr">
         <is>
           <t>コンベア</t>
         </is>
       </c>
-      <c r="M17" s="0" t="inlineStr">
+      <c r="M17" t="inlineStr">
         <is>
           <t>ベルトコンベア</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="C18" s="0" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>機械設備</t>
         </is>
       </c>
-      <c r="D18" s="0" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>衛生機器</t>
         </is>
       </c>
-      <c r="F18" s="0" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t>建築外部</t>
         </is>
       </c>
-      <c r="G18" s="0" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t>看板</t>
         </is>
       </c>
-      <c r="I18" s="0" t="inlineStr">
+      <c r="I18" t="inlineStr">
         <is>
           <t>通信・情報設備</t>
         </is>
       </c>
-      <c r="J18" s="0" t="inlineStr">
+      <c r="J18" t="inlineStr">
         <is>
           <t>情報通信網設備</t>
         </is>
       </c>
-      <c r="L18" s="0" t="inlineStr">
+      <c r="L18" t="inlineStr">
         <is>
           <t>昇降機</t>
         </is>
       </c>
-      <c r="M18" s="0" t="inlineStr">
+      <c r="M18" t="inlineStr">
         <is>
           <t>エレベーター</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="C19" s="0" t="inlineStr">
+      <c r="C19" t="inlineStr">
         <is>
           <t>機械設備</t>
         </is>
       </c>
-      <c r="D19" s="0" t="inlineStr">
+      <c r="D19" t="inlineStr">
         <is>
           <t>給湯機器</t>
         </is>
       </c>
-      <c r="F19" s="0" t="inlineStr">
+      <c r="F19" t="inlineStr">
         <is>
           <t>建築外部</t>
         </is>
       </c>
-      <c r="G19" s="0" t="inlineStr">
+      <c r="G19" t="inlineStr">
         <is>
           <t>煙突</t>
         </is>
       </c>
-      <c r="I19" s="0" t="inlineStr">
+      <c r="I19" t="inlineStr">
         <is>
           <t>通信・情報設備</t>
         </is>
       </c>
-      <c r="J19" s="0" t="inlineStr">
+      <c r="J19" t="inlineStr">
         <is>
           <t>映像音響設備</t>
         </is>
       </c>
-      <c r="L19" s="0" t="inlineStr">
+      <c r="L19" t="inlineStr">
         <is>
           <t>昇降機</t>
         </is>
       </c>
-      <c r="M19" s="0" t="inlineStr">
+      <c r="M19" t="inlineStr">
         <is>
           <t>エスカレーター</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="C20" s="0" t="inlineStr">
+      <c r="C20" t="inlineStr">
         <is>
           <t>機械設備</t>
         </is>
       </c>
-      <c r="D20" s="0" t="inlineStr">
+      <c r="D20" t="inlineStr">
         <is>
           <t>蒸気設備</t>
         </is>
       </c>
-      <c r="F20" s="0" t="inlineStr">
+      <c r="F20" t="inlineStr">
         <is>
           <t>建築外部</t>
         </is>
       </c>
-      <c r="G20" s="0" t="inlineStr">
+      <c r="G20" t="inlineStr">
         <is>
           <t>階段</t>
         </is>
       </c>
-      <c r="I20" s="0" t="inlineStr">
+      <c r="I20" t="inlineStr">
         <is>
           <t>通信・情報設備</t>
         </is>
       </c>
-      <c r="J20" s="0" t="inlineStr">
+      <c r="J20" t="inlineStr">
         <is>
           <t>放送設備</t>
         </is>
       </c>
-      <c r="L20" s="0" t="inlineStr">
+      <c r="L20" t="inlineStr">
         <is>
           <t>昇降機</t>
         </is>
       </c>
-      <c r="M20" s="0" t="inlineStr">
+      <c r="M20" t="inlineStr">
         <is>
           <t>小荷物専用昇降機</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="C21" s="0" t="inlineStr">
+      <c r="C21" t="inlineStr">
         <is>
           <t>機械設備</t>
         </is>
       </c>
-      <c r="D21" s="0" t="inlineStr">
+      <c r="D21" t="inlineStr">
         <is>
           <t>ダクトおよび配管</t>
         </is>
       </c>
-      <c r="F21" s="0" t="inlineStr">
+      <c r="F21" t="inlineStr">
         <is>
           <t>建築外部</t>
         </is>
       </c>
-      <c r="G21" s="0" t="inlineStr">
+      <c r="G21" t="inlineStr">
         <is>
           <t>避難階段</t>
         </is>
       </c>
-      <c r="I21" s="0" t="inlineStr">
+      <c r="I21" t="inlineStr">
         <is>
           <t>通信・情報設備</t>
         </is>
       </c>
-      <c r="J21" s="0" t="inlineStr">
+      <c r="J21" t="inlineStr">
         <is>
           <t>誘導支援設備</t>
         </is>
       </c>
-      <c r="L21" s="0" t="inlineStr">
+      <c r="L21" t="inlineStr">
         <is>
           <t>昇降機</t>
         </is>
       </c>
-      <c r="M21" s="0" t="inlineStr">
+      <c r="M21" t="inlineStr">
         <is>
           <t>簡易リフト</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="C22" s="0" t="inlineStr">
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>機械設備</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>機能水装置</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>建築外部</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>その他付属物</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>通信・情報設備</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>呼出設備</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>シンク</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>調理用シンク</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="C23" t="inlineStr">
         <is>
           <t>防災設備</t>
         </is>
       </c>
-      <c r="D22" s="0" t="inlineStr">
+      <c r="D23" t="inlineStr">
         <is>
           <t>消火設備</t>
         </is>
       </c>
-      <c r="F22" s="0" t="inlineStr">
-        <is>
-          <t>建築外部</t>
-        </is>
-      </c>
-      <c r="G22" s="0" t="inlineStr">
-        <is>
-          <t>その他付属物</t>
-        </is>
-      </c>
-      <c r="I22" s="0" t="inlineStr">
-        <is>
-          <t>通信・情報設備</t>
-        </is>
-      </c>
-      <c r="J22" s="0" t="inlineStr">
-        <is>
-          <t>呼出設備</t>
-        </is>
-      </c>
-      <c r="L22" s="0" t="inlineStr">
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>建物内部</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>基礎</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>防犯管理設備</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>防犯設備</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
         <is>
           <t>シンク</t>
         </is>
       </c>
-      <c r="M22" s="0" t="inlineStr">
-        <is>
-          <t>調理用シンク</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="C23" s="0" t="inlineStr">
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>(船形シンク)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="C24" t="inlineStr">
         <is>
           <t>防災設備</t>
         </is>
       </c>
-      <c r="D23" s="0" t="inlineStr">
+      <c r="D24" t="inlineStr">
         <is>
           <t>排煙設備</t>
         </is>
       </c>
-      <c r="F23" s="0" t="inlineStr">
+      <c r="F24" t="inlineStr">
         <is>
           <t>建物内部</t>
         </is>
       </c>
-      <c r="G23" s="0" t="inlineStr">
-        <is>
-          <t>基礎</t>
-        </is>
-      </c>
-      <c r="I23" s="0" t="inlineStr">
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>内壁</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
         <is>
           <t>防犯管理設備</t>
         </is>
       </c>
-      <c r="J23" s="0" t="inlineStr">
-        <is>
-          <t>防犯設備</t>
-        </is>
-      </c>
-      <c r="L23" s="0" t="inlineStr">
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>監視装置</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
         <is>
           <t>シンク</t>
         </is>
       </c>
-      <c r="M23" s="0" t="inlineStr">
+      <c r="M24" t="inlineStr">
         <is>
           <t>食器洗浄用シンク</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="C24" s="0" t="inlineStr">
+    <row r="25">
+      <c r="C25" t="inlineStr">
         <is>
           <t>防災設備</t>
         </is>
       </c>
-      <c r="D24" s="0" t="inlineStr">
+      <c r="D25" t="inlineStr">
         <is>
           <t>防煙設備</t>
         </is>
       </c>
-      <c r="F24" s="0" t="inlineStr">
+      <c r="F25" t="inlineStr">
         <is>
           <t>建物内部</t>
         </is>
       </c>
-      <c r="G24" s="0" t="inlineStr">
-        <is>
-          <t>内壁</t>
-        </is>
-      </c>
-      <c r="I24" s="0" t="inlineStr">
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>柱</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
         <is>
           <t>防犯管理設備</t>
         </is>
       </c>
-      <c r="J24" s="0" t="inlineStr">
-        <is>
-          <t>監視装置</t>
-        </is>
-      </c>
-      <c r="L24" s="0" t="inlineStr">
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>非常通報装置</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
         <is>
           <t>シンク</t>
         </is>
       </c>
-      <c r="M24" s="0" t="inlineStr">
+      <c r="M25" t="inlineStr">
         <is>
           <t>器具洗浄用シンク</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="C25" s="0" t="inlineStr">
+    <row r="26">
+      <c r="C26" t="inlineStr">
         <is>
           <t>防災設備</t>
         </is>
       </c>
-      <c r="D25" s="0" t="inlineStr">
+      <c r="D26" t="inlineStr">
         <is>
           <t>誘導設備</t>
         </is>
       </c>
-      <c r="F25" s="0" t="inlineStr">
+      <c r="F26" t="inlineStr">
         <is>
           <t>建物内部</t>
         </is>
       </c>
-      <c r="G25" s="0" t="inlineStr">
-        <is>
-          <t>柱</t>
-        </is>
-      </c>
-      <c r="I25" s="0" t="inlineStr">
-        <is>
-          <t>防犯管理設備</t>
-        </is>
-      </c>
-      <c r="J25" s="0" t="inlineStr">
-        <is>
-          <t>非常通報装置</t>
-        </is>
-      </c>
-      <c r="L25" s="0" t="inlineStr">
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>梁</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>雷保護設備</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>避雷針・アンテナ</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
         <is>
           <t>シンク</t>
         </is>
       </c>
-      <c r="M25" s="0" t="inlineStr">
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>(そばシンク)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>搬送設備</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>搬送設備</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>建物内部</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>天井</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>構内配電線路・通信線路設備</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>電気配線</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>シンク</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
         <is>
           <t>浸漬槽</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="C26" s="0" t="inlineStr">
+    <row r="28">
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>厨房設備</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>共用機器</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>建物内部</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>床</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>空気調和等設備</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>熱源機</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>シンク</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>シャワーシンク</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>厨房設備</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>熱調理機器</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>建物内部</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>廊下</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>空気調和等設備</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>冷却塔</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>シンク</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>解凍槽</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>厨房設備</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>下調理機</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>建物内部</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>階段</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>空気調和等設備</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>空調機</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>厨房用台類</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>作業台</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>厨房設備</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>冷却と冷凍・冷蔵設備機器</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>建物内部</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>開き戸</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>空気調和等設備</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>空調配管</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>厨房用台類</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>調理台</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>厨房設備</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>食器洗浄機・消毒機器</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>建物内部</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>引き戸・スライド扉</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>空気調和等設備</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>室外機</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>厨房用台類</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>盛付台</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>厨房設備</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>サービス機器</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>建物内部</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>踏面</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>空気調和等設備</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>ポンプ</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>厨房用台類</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>配膳台</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>厨房設備</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>食品廃棄物など処理機器</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>建物内部</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>蹴上</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>空気調和等設備</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>吸気ファン</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>厨房用台類</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>水切台</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>厨房設備</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>その他の厨房設備</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>建物内部</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>ノンスリップ</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>空気調和等設備</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>排気ファン</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>厨房用台類</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>ダストテーブル</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>ガス設備</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>配管設備</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>建物内部</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>カーテンレール</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>空気調和等設備</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>換気扇</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>厨房用台類</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>移動台</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>ガス設備</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>給湯室等設備</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>建物内部</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>ロールスクリーン・ブラインド</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>空気調和等設備</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>排気フード</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>厨房用台類</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>ソイルドテーブル</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>観測対象</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>観測対象</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>建物内部</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>トイレ</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>空気調和等設備</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>グリス除去装置</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>厨房用台類</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>クリーンテーブル</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>その他設備</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>センサー</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>建物内部</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>浴場・シャワー室</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>空気調和等設備</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>簡易自動消火装置</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>厨房用台類</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>(マーブルテーブル)</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>その他設備</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>プール</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>建物内部</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>洗い場</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>空気調和等設備</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>その他空調設備</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>厨房用台類</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>(ミートブロック)</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>その他設備</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>水槽</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>建物内部</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>手摺</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>給水機器</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>給水タンク</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>厨房用棚類</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>食器戸棚</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>その他設備</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>舞台装置</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>建物内部</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>棚</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>給水機器</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>地下タンク</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>厨房用棚類</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>戸棚</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>その他設備</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>遊具</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>建物外構</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>フェンス</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>給水機器</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>ポンプ</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>厨房用棚類</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>ラック</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>その他設備</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>植栽</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>建物外構</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>門扉</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>給水機器</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>水栓</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>厨房用棚類</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>つり戸棚</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>その他設備</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>その他設備</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>建物外構</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>コンクリート塀・ブロック塀</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>給水機器</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>散水栓</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>厨房用棚類</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>つり棚</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>建物外構</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>舗装・砂利敷</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>給水機器</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>弁</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>レンジ</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>オープントップレンジ</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>建物外構</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>車止め・縁石・ガードポール</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>給水機器</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>その他給水設備</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>レンジ</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>ヒートレンジ</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>建物外構</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>残地・法面</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>排水機器</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>グリーストラップ</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>レンジ</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>フライトップレンジ</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>建物外構</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>倉庫</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>排水機器</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>浄化槽</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>レンジ</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>テーブルレンジ</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>建物外構</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>犬走り</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>排水機器</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>ポンプ</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>レンジ</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>卓上コンロ</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>建物外構</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>植栽</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>排水機器</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>排水溝</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>レンジ</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>ローレンジ</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>建物外構</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>側溝・蓋・枡蓋</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>排水機器</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>排水設備</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>レンジ</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>中華レンジ</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>建物外構</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>その他建物外</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>衛生機器</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>水栓</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>レンジ</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>鋳物コンロ</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>衛生機器</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>自動水栓</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>レンジ</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>電磁調理器</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>衛生機器</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>流し台</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>煮炊釜</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>回転釜</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>衛生機器</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>鏡</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>煮炊釜</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>ティルティングパン</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>衛生機器</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>水石鹸入れ</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>煮炊釜</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>(麺かまど)</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>衛生機器</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>洋式便器</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>煮炊釜</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>その他煮炊き釜</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>衛生機器</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>和式便器</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>加熱庫</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>オーブン</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>衛生機器</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>小便器</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>加熱庫</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>コンベクションオーブン</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>衛生機器</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>温水洗浄便座</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>加熱庫</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>スチームコンベクションオーブン</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>衛生機器</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>暖房便座・便座</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>加熱庫</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>電子レンジ</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>衛生機器</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>手洗器・洗濯流し(SK)</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>焼物器</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>(グリラー)</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>衛生機器</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>ペーパーホルダー</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>焼物器</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>(サラマンダー)</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>衛生機器</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>殺菌庫</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>焼物器</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>(ベイクオーブン)</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>衛生機器</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>その他衛生器具</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>焼物器</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>(ピザオーブン)</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>給湯機器</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>湯沸器</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>焼物器</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>(魚焼機)</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>給湯機器</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>ポンプ</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>揚物器</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>フライヤー</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>蒸気設備</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>蒸気ボイラー</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>揚物器</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>プレッシャーフライヤー</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>蒸気設備</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>減圧弁</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>揚物器</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>連続式フライヤー</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>蒸気設備</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>安全装置</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>揚物器</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>新油タンク</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>ダクトおよび配管</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>空調ダクト</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>揚物器</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>廃油タンク</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>ダクトおよび配管</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>換気ダクト</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>蒸し器</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>無圧式スチーマー</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>ダクトおよび配管</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>給水管</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>蒸し器</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>加圧式スチーマー</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>ダクトおよび配管</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>排水管</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>炊飯器</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>立体炊飯器</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>ダクトおよび配管</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>蒸気配管</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>炊飯器</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>連続炊飯装置</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>機能水装置</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>全自動軟水装置</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>炊飯器</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>電気炊飯器</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>機能水装置</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>微酸性水生成器</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>炊飯器</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>炊飯ジャー</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>消火設備</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>消防設備</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>炊飯器</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>保温ジャー</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>消火設備</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>ポンプ</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>食材洗浄機</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>球根皮むき機</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>消火設備</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>その他消火設備</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>食材洗浄機</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>野菜洗浄機</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>消火設備</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>防火扉</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>食材洗浄機</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>脱水機</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>消火設備</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>防火シャッター</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>食材洗浄機</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>水圧式洗米機</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>消火設備</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>防火ダンパー</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>食材洗浄機</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>連続洗米機</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>消火設備</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>防火クロススクリーン</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>食材洗浄機</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>自動計量洗米機</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>消火設備</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>ドレンチャー</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>切裁機</t>
+        </is>
+      </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>野菜切裁機</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>消火設備</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>その他防火設備</t>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>切裁機</t>
+        </is>
+      </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>フードスライサー</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>排煙設備</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>排煙ファン</t>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>切裁機</t>
+        </is>
+      </c>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>さいの目切り機</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>排煙設備</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>排煙口</t>
+        </is>
+      </c>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>切裁機</t>
+        </is>
+      </c>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>せん切り機</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>排煙設備</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>その他排煙設備</t>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>切裁機</t>
+        </is>
+      </c>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>フードカッター</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>防煙設備</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>防煙壁</t>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>切裁機</t>
+        </is>
+      </c>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>(ミートチョッパー)</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>防煙設備</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>その他防煙設備</t>
+        </is>
+      </c>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>切裁機</t>
+        </is>
+      </c>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>(スライサー)</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>誘導設備</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>非常用照明装置</t>
+        </is>
+      </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>切裁機</t>
+        </is>
+      </c>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>(ミートソー)</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>誘導設備</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>誘導灯</t>
+        </is>
+      </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>切裁機</t>
+        </is>
+      </c>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>(テンダライザー)</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="I95" t="inlineStr">
         <is>
           <t>搬送設備</t>
         </is>
       </c>
-      <c r="D26" s="0" t="inlineStr">
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>コンベア</t>
+        </is>
+      </c>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>切裁機</t>
+        </is>
+      </c>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>カッターミキサー</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="I96" t="inlineStr">
         <is>
           <t>搬送設備</t>
         </is>
       </c>
-      <c r="F26" s="0" t="inlineStr">
-        <is>
-          <t>建物内部</t>
-        </is>
-      </c>
-      <c r="G26" s="0" t="inlineStr">
-        <is>
-          <t>梁</t>
-        </is>
-      </c>
-      <c r="I26" s="0" t="inlineStr">
-        <is>
-          <t>雷保護設備</t>
-        </is>
-      </c>
-      <c r="J26" s="0" t="inlineStr">
-        <is>
-          <t>避雷針・アンテナ</t>
-        </is>
-      </c>
-      <c r="L26" s="0" t="inlineStr">
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>米サイロ</t>
+        </is>
+      </c>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>切裁機</t>
+        </is>
+      </c>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>その他の切裁機</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>搬送設備</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>昇降機</t>
+        </is>
+      </c>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>かくはん混合機</t>
+        </is>
+      </c>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>立型フードミキサー</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>共用機器</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
         <is>
           <t>シンク</t>
         </is>
       </c>
-      <c r="M26" s="0" t="inlineStr">
-        <is>
-          <t>シャワーシンク</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="C27" s="0" t="inlineStr">
-        <is>
-          <t>厨房設備</t>
-        </is>
-      </c>
-      <c r="D27" s="0" t="inlineStr">
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>かくはん混合機</t>
+        </is>
+      </c>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>横型フードミキサー</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="I99" t="inlineStr">
         <is>
           <t>共用機器</t>
         </is>
       </c>
-      <c r="F27" s="0" t="inlineStr">
-        <is>
-          <t>建物内部</t>
-        </is>
-      </c>
-      <c r="G27" s="0" t="inlineStr">
-        <is>
-          <t>天井</t>
-        </is>
-      </c>
-      <c r="I27" s="0" t="inlineStr">
-        <is>
-          <t>構内配電線路・通信線路設備</t>
-        </is>
-      </c>
-      <c r="J27" s="0" t="inlineStr">
-        <is>
-          <t>電気配線</t>
-        </is>
-      </c>
-      <c r="L27" s="0" t="inlineStr">
-        <is>
-          <t>シンク</t>
-        </is>
-      </c>
-      <c r="M27" s="0" t="inlineStr">
-        <is>
-          <t>解凍槽</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="C28" s="0" t="inlineStr">
-        <is>
-          <t>厨房設備</t>
-        </is>
-      </c>
-      <c r="D28" s="0" t="inlineStr">
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>厨房用台類</t>
+        </is>
+      </c>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>かくはん混合機</t>
+        </is>
+      </c>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>ブレンダー</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>共用機器</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>厨房用棚類</t>
+        </is>
+      </c>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>かくはん混合機</t>
+        </is>
+      </c>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>高速度ミキサー</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="I101" t="inlineStr">
         <is>
           <t>熱調理機器</t>
         </is>
       </c>
-      <c r="F28" s="0" t="inlineStr">
-        <is>
-          <t>建物内部</t>
-        </is>
-      </c>
-      <c r="G28" s="0" t="inlineStr">
-        <is>
-          <t>床</t>
-        </is>
-      </c>
-      <c r="I28" s="0" t="inlineStr">
-        <is>
-          <t>空気調和等設備</t>
-        </is>
-      </c>
-      <c r="J28" s="0" t="inlineStr">
-        <is>
-          <t>熱源機</t>
-        </is>
-      </c>
-      <c r="L28" s="0" t="inlineStr">
-        <is>
-          <t>厨房用台類</t>
-        </is>
-      </c>
-      <c r="M28" s="0" t="inlineStr">
-        <is>
-          <t>作業台</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="C29" s="0" t="inlineStr">
-        <is>
-          <t>厨房設備</t>
-        </is>
-      </c>
-      <c r="D29" s="0" t="inlineStr">
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>レンジ</t>
+        </is>
+      </c>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>かくはん混合機</t>
+        </is>
+      </c>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>その他のミキサー</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>熱調理機器</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>煮炊釜</t>
+        </is>
+      </c>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>かくはん混合機</t>
+        </is>
+      </c>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>(らいかい機)</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>熱調理機器</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>加熱庫</t>
+        </is>
+      </c>
+      <c r="L103" t="inlineStr">
+        <is>
+          <t>かくはん混合機</t>
+        </is>
+      </c>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>(いもつぶし機)</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>熱調理機器</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>焼物器</t>
+        </is>
+      </c>
+      <c r="L104" t="inlineStr">
+        <is>
+          <t>食品成型機</t>
+        </is>
+      </c>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>食品成型機</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>熱調理機器</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>揚物器</t>
+        </is>
+      </c>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>食品成型機</t>
+        </is>
+      </c>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>粉付け機</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>熱調理機器</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>蒸し器</t>
+        </is>
+      </c>
+      <c r="L106" t="inlineStr">
+        <is>
+          <t>食品成型機</t>
+        </is>
+      </c>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>(製麺機)</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>熱調理機器</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>炊飯器</t>
+        </is>
+      </c>
+      <c r="L107" t="inlineStr">
+        <is>
+          <t>その他の下調理機</t>
+        </is>
+      </c>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>缶切り機</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>熱調理機器</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>その他の熱調理機</t>
+        </is>
+      </c>
+      <c r="L108" t="inlineStr">
+        <is>
+          <t>その他の下調理機</t>
+        </is>
+      </c>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>その他の下調理機</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="I109" t="inlineStr">
         <is>
           <t>下調理機</t>
         </is>
       </c>
-      <c r="F29" s="0" t="inlineStr">
-        <is>
-          <t>建物内部</t>
-        </is>
-      </c>
-      <c r="G29" s="0" t="inlineStr">
-        <is>
-          <t>廊下</t>
-        </is>
-      </c>
-      <c r="I29" s="0" t="inlineStr">
-        <is>
-          <t>空気調和等設備</t>
-        </is>
-      </c>
-      <c r="J29" s="0" t="inlineStr">
-        <is>
-          <t>冷却塔</t>
-        </is>
-      </c>
-      <c r="L29" s="0" t="inlineStr">
-        <is>
-          <t>厨房用台類</t>
-        </is>
-      </c>
-      <c r="M29" s="0" t="inlineStr">
-        <is>
-          <t>調理台</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="C30" s="0" t="inlineStr">
-        <is>
-          <t>厨房設備</t>
-        </is>
-      </c>
-      <c r="D30" s="0" t="inlineStr">
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>食材洗浄機</t>
+        </is>
+      </c>
+      <c r="L109" t="inlineStr">
+        <is>
+          <t>低温貯蔵保管機器</t>
+        </is>
+      </c>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>プレハブ式</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>下調理機</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>切裁機</t>
+        </is>
+      </c>
+      <c r="L110" t="inlineStr">
+        <is>
+          <t>低温貯蔵保管機器</t>
+        </is>
+      </c>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>リーチイン式</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>下調理機</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>かくはん混合機</t>
+        </is>
+      </c>
+      <c r="L111" t="inlineStr">
+        <is>
+          <t>低温貯蔵保管機器</t>
+        </is>
+      </c>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>⽜乳保冷庫</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>下調理機</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>食品成型機</t>
+        </is>
+      </c>
+      <c r="L112" t="inlineStr">
+        <is>
+          <t>鮮度向上生産機器</t>
+        </is>
+      </c>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>急速冷凍庫</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>下調理機</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>その他の下調理機</t>
+        </is>
+      </c>
+      <c r="L113" t="inlineStr">
+        <is>
+          <t>鮮度向上生産機器</t>
+        </is>
+      </c>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>ブラストチラー</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="I114" t="inlineStr">
         <is>
           <t>冷却と冷凍・冷蔵設備機器</t>
         </is>
       </c>
-      <c r="F30" s="0" t="inlineStr">
-        <is>
-          <t>建物内部</t>
-        </is>
-      </c>
-      <c r="G30" s="0" t="inlineStr">
-        <is>
-          <t>階段</t>
-        </is>
-      </c>
-      <c r="I30" s="0" t="inlineStr">
-        <is>
-          <t>空気調和等設備</t>
-        </is>
-      </c>
-      <c r="J30" s="0" t="inlineStr">
-        <is>
-          <t>空調機</t>
-        </is>
-      </c>
-      <c r="L30" s="0" t="inlineStr">
-        <is>
-          <t>厨房用台類</t>
-        </is>
-      </c>
-      <c r="M30" s="0" t="inlineStr">
-        <is>
-          <t>盛付台</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="C31" s="0" t="inlineStr">
-        <is>
-          <t>厨房設備</t>
-        </is>
-      </c>
-      <c r="D31" s="0" t="inlineStr">
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>低温貯蔵保管機器</t>
+        </is>
+      </c>
+      <c r="L114" t="inlineStr">
+        <is>
+          <t>鮮度向上生産機器</t>
+        </is>
+      </c>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>真空冷却機</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>冷却と冷凍・冷蔵設備機器</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>鮮度向上生産機器</t>
+        </is>
+      </c>
+      <c r="L115" t="inlineStr">
+        <is>
+          <t>鮮度向上生産機器</t>
+        </is>
+      </c>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>チラー用給水タンク</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>冷却と冷凍・冷蔵設備機器</t>
+        </is>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>低温物流機器</t>
+        </is>
+      </c>
+      <c r="L116" t="inlineStr">
+        <is>
+          <t>鮮度向上生産機器</t>
+        </is>
+      </c>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>真空冷却機用チラー</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>冷却と冷凍・冷蔵設備機器</t>
+        </is>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>(陳列・展示機器)</t>
+        </is>
+      </c>
+      <c r="L117" t="inlineStr">
+        <is>
+          <t>低温物流機器</t>
+        </is>
+      </c>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>コールドロールボックス</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>冷却と冷凍・冷蔵設備機器</t>
+        </is>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>解凍機器</t>
+        </is>
+      </c>
+      <c r="L118" t="inlineStr">
+        <is>
+          <t>(陳列・展示機器)</t>
+        </is>
+      </c>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>(冷凍ショーケース)</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>冷却と冷凍・冷蔵設備機器</t>
+        </is>
+      </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>製氷機</t>
+        </is>
+      </c>
+      <c r="L119" t="inlineStr">
+        <is>
+          <t>(陳列・展示機器)</t>
+        </is>
+      </c>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>(氷温ショーケース)</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>冷却と冷凍・冷蔵設備機器</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>その他の冷却冷凍冷蔵設備</t>
+        </is>
+      </c>
+      <c r="L120" t="inlineStr">
+        <is>
+          <t>(陳列・展示機器)</t>
+        </is>
+      </c>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>(冷蔵ショーケース)</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="I121" t="inlineStr">
         <is>
           <t>食器洗浄機・消毒機器</t>
         </is>
       </c>
-      <c r="F31" s="0" t="inlineStr">
-        <is>
-          <t>建物内部</t>
-        </is>
-      </c>
-      <c r="G31" s="0" t="inlineStr">
-        <is>
-          <t>開き戸</t>
-        </is>
-      </c>
-      <c r="I31" s="0" t="inlineStr">
-        <is>
-          <t>空気調和等設備</t>
-        </is>
-      </c>
-      <c r="J31" s="0" t="inlineStr">
-        <is>
-          <t>空調配管</t>
-        </is>
-      </c>
-      <c r="L31" s="0" t="inlineStr">
-        <is>
-          <t>厨房用台類</t>
-        </is>
-      </c>
-      <c r="M31" s="0" t="inlineStr">
-        <is>
-          <t>配膳台</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="C32" s="0" t="inlineStr">
-        <is>
-          <t>厨房設備</t>
-        </is>
-      </c>
-      <c r="D32" s="0" t="inlineStr">
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>食器洗浄機</t>
+        </is>
+      </c>
+      <c r="L121" t="inlineStr">
+        <is>
+          <t>(陳列・展示機器)</t>
+        </is>
+      </c>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>(冷水ショーケース)</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>食器洗浄機・消毒機器</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>消毒機器</t>
+        </is>
+      </c>
+      <c r="L122" t="inlineStr">
+        <is>
+          <t>食器洗浄機</t>
+        </is>
+      </c>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>ドアタイプ洗浄機</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="I123" t="inlineStr">
         <is>
           <t>サービス機器</t>
         </is>
       </c>
-      <c r="F32" s="0" t="inlineStr">
-        <is>
-          <t>建物内部</t>
-        </is>
-      </c>
-      <c r="G32" s="0" t="inlineStr">
-        <is>
-          <t>引き戸・スライド扉</t>
-        </is>
-      </c>
-      <c r="I32" s="0" t="inlineStr">
-        <is>
-          <t>空気調和等設備</t>
-        </is>
-      </c>
-      <c r="J32" s="0" t="inlineStr">
-        <is>
-          <t>室外機</t>
-        </is>
-      </c>
-      <c r="L32" s="0" t="inlineStr">
-        <is>
-          <t>厨房用台類</t>
-        </is>
-      </c>
-      <c r="M32" s="0" t="inlineStr">
-        <is>
-          <t>水切台</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="C33" s="0" t="inlineStr">
-        <is>
-          <t>厨房設備</t>
-        </is>
-      </c>
-      <c r="D33" s="0" t="inlineStr">
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>保温機器</t>
+        </is>
+      </c>
+      <c r="L123" t="inlineStr">
+        <is>
+          <t>食器洗浄機</t>
+        </is>
+      </c>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>アンダーカウンタタイプ洗浄機</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>サービス機器</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>ベーカリー関連機器</t>
+        </is>
+      </c>
+      <c r="L124" t="inlineStr">
+        <is>
+          <t>食器洗浄機</t>
+        </is>
+      </c>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>フードタイプ洗浄機</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>サービス機器</t>
+        </is>
+      </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>配膳車・下膳車</t>
+        </is>
+      </c>
+      <c r="L125" t="inlineStr">
+        <is>
+          <t>食器洗浄機</t>
+        </is>
+      </c>
+      <c r="M125" t="inlineStr">
+        <is>
+          <t>コンベアタイプ洗浄機</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="I126" t="inlineStr">
         <is>
           <t>食品廃棄物など処理機器</t>
         </is>
       </c>
-      <c r="F33" s="0" t="inlineStr">
-        <is>
-          <t>建物内部</t>
-        </is>
-      </c>
-      <c r="G33" s="0" t="inlineStr">
-        <is>
-          <t>踏面</t>
-        </is>
-      </c>
-      <c r="I33" s="0" t="inlineStr">
-        <is>
-          <t>空気調和等設備</t>
-        </is>
-      </c>
-      <c r="J33" s="0" t="inlineStr">
-        <is>
-          <t>ポンプ</t>
-        </is>
-      </c>
-      <c r="L33" s="0" t="inlineStr">
-        <is>
-          <t>厨房用台類</t>
-        </is>
-      </c>
-      <c r="M33" s="0" t="inlineStr">
-        <is>
-          <t>ダストテーブル</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="C34" s="0" t="inlineStr">
-        <is>
-          <t>ガス設備</t>
-        </is>
-      </c>
-      <c r="D34" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">配管設備 </t>
-        </is>
-      </c>
-      <c r="F34" s="0" t="inlineStr">
-        <is>
-          <t>建物内部</t>
-        </is>
-      </c>
-      <c r="G34" s="0" t="inlineStr">
-        <is>
-          <t>蹴上</t>
-        </is>
-      </c>
-      <c r="I34" s="0" t="inlineStr">
-        <is>
-          <t>空気調和等設備</t>
-        </is>
-      </c>
-      <c r="J34" s="0" t="inlineStr">
-        <is>
-          <t>吸気ファン</t>
-        </is>
-      </c>
-      <c r="L34" s="0" t="inlineStr">
-        <is>
-          <t>厨房用台類</t>
-        </is>
-      </c>
-      <c r="M34" s="0" t="inlineStr">
-        <is>
-          <t>移動台</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="C35" s="0" t="inlineStr">
-        <is>
-          <t>ガス設備</t>
-        </is>
-      </c>
-      <c r="D35" s="0" t="inlineStr">
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>生ごみ処理</t>
+        </is>
+      </c>
+      <c r="L126" t="inlineStr">
+        <is>
+          <t>食器洗浄機</t>
+        </is>
+      </c>
+      <c r="M126" t="inlineStr">
+        <is>
+          <t>かき上げタイプ洗浄機</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>食品廃棄物など処理機器</t>
+        </is>
+      </c>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>コンパクター</t>
+        </is>
+      </c>
+      <c r="L127" t="inlineStr">
+        <is>
+          <t>食器洗浄機</t>
+        </is>
+      </c>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>ラウンドタイプ洗浄機</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>食品廃棄物など処理機器</t>
+        </is>
+      </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>パルパーエストラシステム</t>
+        </is>
+      </c>
+      <c r="L128" t="inlineStr">
+        <is>
+          <t>食器洗浄機</t>
+        </is>
+      </c>
+      <c r="M128" t="inlineStr">
+        <is>
+          <t>超音波洗浄機</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>その他の厨房設備</t>
+        </is>
+      </c>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>金属探知機</t>
+        </is>
+      </c>
+      <c r="L129" t="inlineStr">
+        <is>
+          <t>食器洗浄機</t>
+        </is>
+      </c>
+      <c r="M129" t="inlineStr">
+        <is>
+          <t>その他の食器洗浄機</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>配管設備</t>
+        </is>
+      </c>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>ガス栓</t>
+        </is>
+      </c>
+      <c r="L130" t="inlineStr">
+        <is>
+          <t>消毒機器</t>
+        </is>
+      </c>
+      <c r="M130" t="inlineStr">
+        <is>
+          <t>棚式消毒保管庫</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>配管設備</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>ガス接続具</t>
+        </is>
+      </c>
+      <c r="L131" t="inlineStr">
+        <is>
+          <t>消毒機器</t>
+        </is>
+      </c>
+      <c r="M131" t="inlineStr">
+        <is>
+          <t>カートイン式消毒保管庫</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>配管設備</t>
+        </is>
+      </c>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>ガス漏れ警報器等</t>
+        </is>
+      </c>
+      <c r="L132" t="inlineStr">
+        <is>
+          <t>消毒機器</t>
+        </is>
+      </c>
+      <c r="M132" t="inlineStr">
+        <is>
+          <t>天吊り式消毒装置</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="I133" t="inlineStr">
         <is>
           <t>給湯室等設備</t>
         </is>
       </c>
-      <c r="F35" s="0" t="inlineStr">
-        <is>
-          <t>建物内部</t>
-        </is>
-      </c>
-      <c r="G35" s="0" t="inlineStr">
-        <is>
-          <t>ノンスリップ</t>
-        </is>
-      </c>
-      <c r="I35" s="0" t="inlineStr">
-        <is>
-          <t>空気調和等設備</t>
-        </is>
-      </c>
-      <c r="J35" s="0" t="inlineStr">
-        <is>
-          <t>排気ファン</t>
-        </is>
-      </c>
-      <c r="L35" s="0" t="inlineStr">
-        <is>
-          <t>厨房用台類</t>
-        </is>
-      </c>
-      <c r="M35" s="0" t="inlineStr">
-        <is>
-          <t>ソイルドテーブル</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="C36" s="0" t="inlineStr">
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>ガス器具</t>
+        </is>
+      </c>
+      <c r="L133" t="inlineStr">
+        <is>
+          <t>保温機器</t>
+        </is>
+      </c>
+      <c r="M133" t="inlineStr">
+        <is>
+          <t>(ペンマリー)</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="I134" t="inlineStr">
         <is>
           <t>観測対象</t>
         </is>
       </c>
-      <c r="D36" s="0" t="inlineStr">
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>空間</t>
+        </is>
+      </c>
+      <c r="L134" t="inlineStr">
+        <is>
+          <t>保温機器</t>
+        </is>
+      </c>
+      <c r="M134" t="inlineStr">
+        <is>
+          <t>ウオーマーテーブル</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="I135" t="inlineStr">
         <is>
           <t>観測対象</t>
         </is>
       </c>
-      <c r="F36" s="0" t="inlineStr">
-        <is>
-          <t>建物内部</t>
-        </is>
-      </c>
-      <c r="G36" s="0" t="inlineStr">
-        <is>
-          <t>カーテンレール</t>
-        </is>
-      </c>
-      <c r="I36" s="0" t="inlineStr">
-        <is>
-          <t>空気調和等設備</t>
-        </is>
-      </c>
-      <c r="J36" s="0" t="inlineStr">
-        <is>
-          <t>換気扇</t>
-        </is>
-      </c>
-      <c r="L36" s="0" t="inlineStr">
-        <is>
-          <t>厨房用台類</t>
-        </is>
-      </c>
-      <c r="M36" s="0" t="inlineStr">
-        <is>
-          <t>クリーンテーブル</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="C37" s="0" t="inlineStr">
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>水</t>
+        </is>
+      </c>
+      <c r="L135" t="inlineStr">
+        <is>
+          <t>保温機器</t>
+        </is>
+      </c>
+      <c r="M135" t="inlineStr">
+        <is>
+          <t>温蔵庫</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>観測対象</t>
+        </is>
+      </c>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>蒸気</t>
+        </is>
+      </c>
+      <c r="L136" t="inlineStr">
+        <is>
+          <t>保温機器</t>
+        </is>
+      </c>
+      <c r="M136" t="inlineStr">
+        <is>
+          <t>その他の保温機器</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>観測対象</t>
+        </is>
+      </c>
+      <c r="J137" t="inlineStr">
+        <is>
+          <t>(食品)</t>
+        </is>
+      </c>
+      <c r="L137" t="inlineStr">
+        <is>
+          <t>ベーカリー関連機器</t>
+        </is>
+      </c>
+      <c r="M137" t="inlineStr">
+        <is>
+          <t>ドーナツフライヤー</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>センサー</t>
+        </is>
+      </c>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>センサー</t>
+        </is>
+      </c>
+      <c r="L138" t="inlineStr">
+        <is>
+          <t>ベーカリー関連機器</t>
+        </is>
+      </c>
+      <c r="M138" t="inlineStr">
+        <is>
+          <t>ホイロ</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>センサー</t>
+        </is>
+      </c>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>秤</t>
+        </is>
+      </c>
+      <c r="L139" t="inlineStr">
+        <is>
+          <t>ベーカリー関連機器</t>
+        </is>
+      </c>
+      <c r="M139" t="inlineStr">
+        <is>
+          <t>ドゥコンディショナー</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>プール</t>
+        </is>
+      </c>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>プール</t>
+        </is>
+      </c>
+      <c r="L140" t="inlineStr">
+        <is>
+          <t>ベーカリー関連機器</t>
+        </is>
+      </c>
+      <c r="M140" t="inlineStr">
+        <is>
+          <t>解凍庫</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>プール</t>
+        </is>
+      </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>プール設備</t>
+        </is>
+      </c>
+      <c r="L141" t="inlineStr">
+        <is>
+          <t>ベーカリー関連機器</t>
+        </is>
+      </c>
+      <c r="M141" t="inlineStr">
+        <is>
+          <t>ラックカート</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>水槽</t>
+        </is>
+      </c>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>水槽</t>
+        </is>
+      </c>
+      <c r="L142" t="inlineStr">
+        <is>
+          <t>ベーカリー関連機器</t>
+        </is>
+      </c>
+      <c r="M142" t="inlineStr">
+        <is>
+          <t>トンボラック</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>舞台装置</t>
+        </is>
+      </c>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>舞台機構</t>
+        </is>
+      </c>
+      <c r="L143" t="inlineStr">
+        <is>
+          <t>ベーカリー関連機器</t>
+        </is>
+      </c>
+      <c r="M143" t="inlineStr">
+        <is>
+          <t>スパイラルミキサー</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>舞台装置</t>
+        </is>
+      </c>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>舞台照明</t>
+        </is>
+      </c>
+      <c r="L144" t="inlineStr">
+        <is>
+          <t>ベーカリー関連機器</t>
+        </is>
+      </c>
+      <c r="M144" t="inlineStr">
+        <is>
+          <t>成形機</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>舞台装置</t>
+        </is>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>舞台音響</t>
+        </is>
+      </c>
+      <c r="L145" t="inlineStr">
+        <is>
+          <t>ベーカリー関連機器</t>
+        </is>
+      </c>
+      <c r="M145" t="inlineStr">
+        <is>
+          <t>分割丸目機</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>舞台装置</t>
+        </is>
+      </c>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>舞台装置</t>
+        </is>
+      </c>
+      <c r="L146" t="inlineStr">
+        <is>
+          <t>ベーカリー関連機器</t>
+        </is>
+      </c>
+      <c r="M146" t="inlineStr">
+        <is>
+          <t>リバースシート</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>遊具</t>
+        </is>
+      </c>
+      <c r="J147" t="inlineStr">
+        <is>
+          <t>遊具</t>
+        </is>
+      </c>
+      <c r="L147" t="inlineStr">
+        <is>
+          <t>ベーカリー関連機器</t>
+        </is>
+      </c>
+      <c r="M147" t="inlineStr">
+        <is>
+          <t>パンスライサー</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>植栽</t>
+        </is>
+      </c>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>植栽</t>
+        </is>
+      </c>
+      <c r="L148" t="inlineStr">
+        <is>
+          <t>ベーカリー関連機器</t>
+        </is>
+      </c>
+      <c r="M148" t="inlineStr">
+        <is>
+          <t>冷温水水量計</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="I149" t="inlineStr">
         <is>
           <t>その他設備</t>
         </is>
       </c>
-      <c r="D37" s="0" t="inlineStr">
-        <is>
-          <t>センサー</t>
-        </is>
-      </c>
-      <c r="F37" s="0" t="inlineStr">
-        <is>
-          <t>建物内部</t>
-        </is>
-      </c>
-      <c r="G37" s="0" t="inlineStr">
-        <is>
-          <t>ロールスクリーン・ブラインド</t>
-        </is>
-      </c>
-      <c r="I37" s="0" t="inlineStr">
-        <is>
-          <t>空気調和等設備</t>
-        </is>
-      </c>
-      <c r="J37" s="0" t="inlineStr">
-        <is>
-          <t>排気フード</t>
-        </is>
-      </c>
-      <c r="L37" s="0" t="inlineStr">
-        <is>
-          <t>厨房用棚類</t>
-        </is>
-      </c>
-      <c r="M37" s="0" t="inlineStr">
-        <is>
-          <t>食器戸棚</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="C38" s="0" t="inlineStr">
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>椅子</t>
+        </is>
+      </c>
+      <c r="L149" t="inlineStr">
+        <is>
+          <t>配膳車・下膳車</t>
+        </is>
+      </c>
+      <c r="M149" t="inlineStr">
+        <is>
+          <t>コンテナ</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="I150" t="inlineStr">
         <is>
           <t>その他設備</t>
         </is>
       </c>
-      <c r="D38" s="0" t="inlineStr">
-        <is>
-          <t>プール</t>
-        </is>
-      </c>
-      <c r="F38" s="0" t="inlineStr">
-        <is>
-          <t>建物内部</t>
-        </is>
-      </c>
-      <c r="G38" s="0" t="inlineStr">
-        <is>
-          <t>トイレ</t>
-        </is>
-      </c>
-      <c r="I38" s="0" t="inlineStr">
-        <is>
-          <t>空気調和等設備</t>
-        </is>
-      </c>
-      <c r="J38" s="0" t="inlineStr">
-        <is>
-          <t>グリス除去装置</t>
-        </is>
-      </c>
-      <c r="L38" s="0" t="inlineStr">
-        <is>
-          <t>厨房用棚類</t>
-        </is>
-      </c>
-      <c r="M38" s="0" t="inlineStr">
-        <is>
-          <t>戸棚</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="C39" s="0" t="inlineStr">
+      <c r="J150" t="inlineStr">
         <is>
           <t>その他設備</t>
         </is>
       </c>
-      <c r="D39" s="0" t="inlineStr">
-        <is>
-          <t>水槽</t>
-        </is>
-      </c>
-      <c r="F39" s="0" t="inlineStr">
-        <is>
-          <t>建物内部</t>
-        </is>
-      </c>
-      <c r="G39" s="0" t="inlineStr">
-        <is>
-          <t>浴場・シャワー室</t>
-        </is>
-      </c>
-      <c r="I39" s="0" t="inlineStr">
-        <is>
-          <t>空気調和等設備</t>
-        </is>
-      </c>
-      <c r="J39" s="0" t="inlineStr">
-        <is>
-          <t>簡易自動消火装置</t>
-        </is>
-      </c>
-      <c r="L39" s="0" t="inlineStr">
-        <is>
-          <t>厨房用棚類</t>
-        </is>
-      </c>
-      <c r="M39" s="0" t="inlineStr">
-        <is>
-          <t>ラック</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="C40" s="0" t="inlineStr">
-        <is>
-          <t>その他設備</t>
-        </is>
-      </c>
-      <c r="D40" s="0" t="inlineStr">
-        <is>
-          <t>舞台装置</t>
-        </is>
-      </c>
-      <c r="F40" s="0" t="inlineStr">
-        <is>
-          <t>建物内部</t>
-        </is>
-      </c>
-      <c r="G40" s="0" t="inlineStr">
-        <is>
-          <t>洗い場</t>
-        </is>
-      </c>
-      <c r="I40" s="0" t="inlineStr">
-        <is>
-          <t>空気調和等設備</t>
-        </is>
-      </c>
-      <c r="J40" s="0" t="inlineStr">
-        <is>
-          <t>その他空調設備</t>
-        </is>
-      </c>
-      <c r="L40" s="0" t="inlineStr">
-        <is>
-          <t>厨房用棚類</t>
-        </is>
-      </c>
-      <c r="M40" s="0" t="inlineStr">
-        <is>
-          <t>つり戸棚</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="C41" s="0" t="inlineStr">
-        <is>
-          <t>その他設備</t>
-        </is>
-      </c>
-      <c r="D41" s="0" t="inlineStr">
-        <is>
-          <t>遊具</t>
-        </is>
-      </c>
-      <c r="F41" s="0" t="inlineStr">
-        <is>
-          <t>建物内部</t>
-        </is>
-      </c>
-      <c r="G41" s="0" t="inlineStr">
-        <is>
-          <t>手摺</t>
-        </is>
-      </c>
-      <c r="I41" s="0" t="inlineStr">
-        <is>
-          <t>給水機器</t>
-        </is>
-      </c>
-      <c r="J41" s="0" t="inlineStr">
-        <is>
-          <t>給水タンク</t>
-        </is>
-      </c>
-      <c r="L41" s="0" t="inlineStr">
-        <is>
-          <t>厨房用棚類</t>
-        </is>
-      </c>
-      <c r="M41" s="0" t="inlineStr">
-        <is>
-          <t>つり棚</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="C42" s="0" t="inlineStr">
-        <is>
-          <t>その他設備</t>
-        </is>
-      </c>
-      <c r="D42" s="0" t="inlineStr">
-        <is>
-          <t>植栽</t>
-        </is>
-      </c>
-      <c r="F42" s="0" t="inlineStr">
-        <is>
-          <t>建物内部</t>
-        </is>
-      </c>
-      <c r="G42" s="0" t="inlineStr">
-        <is>
-          <t>棚</t>
-        </is>
-      </c>
-      <c r="I42" s="0" t="inlineStr">
-        <is>
-          <t>給水機器</t>
-        </is>
-      </c>
-      <c r="J42" s="0" t="inlineStr">
-        <is>
-          <t>地下タンク</t>
-        </is>
-      </c>
-      <c r="L42" s="0" t="inlineStr">
-        <is>
-          <t>レンジ</t>
-        </is>
-      </c>
-      <c r="M42" s="0" t="inlineStr">
-        <is>
-          <t>オープントップレンジ</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="C43" s="0" t="inlineStr">
-        <is>
-          <t>その他設備</t>
-        </is>
-      </c>
-      <c r="D43" s="0" t="inlineStr">
-        <is>
-          <t>その他設備</t>
-        </is>
-      </c>
-      <c r="F43" s="0" t="inlineStr">
-        <is>
-          <t>建物外構</t>
-        </is>
-      </c>
-      <c r="G43" s="0" t="inlineStr">
-        <is>
-          <t>フェンス</t>
-        </is>
-      </c>
-      <c r="I43" s="0" t="inlineStr">
-        <is>
-          <t>給水機器</t>
-        </is>
-      </c>
-      <c r="J43" s="0" t="inlineStr">
-        <is>
-          <t>ポンプ</t>
-        </is>
-      </c>
-      <c r="L43" s="0" t="inlineStr">
-        <is>
-          <t>レンジ</t>
-        </is>
-      </c>
-      <c r="M43" s="0" t="inlineStr">
-        <is>
-          <t>ヒートレンジ</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="F44" s="0" t="inlineStr">
-        <is>
-          <t>建物外構</t>
-        </is>
-      </c>
-      <c r="G44" s="0" t="inlineStr">
-        <is>
-          <t>門扉</t>
-        </is>
-      </c>
-      <c r="I44" s="0" t="inlineStr">
-        <is>
-          <t>給水機器</t>
-        </is>
-      </c>
-      <c r="J44" s="0" t="inlineStr">
-        <is>
-          <t>水栓</t>
-        </is>
-      </c>
-      <c r="L44" s="0" t="inlineStr">
-        <is>
-          <t>レンジ</t>
-        </is>
-      </c>
-      <c r="M44" s="0" t="inlineStr">
-        <is>
-          <t>フライトップレンジ</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="F45" s="0" t="inlineStr">
-        <is>
-          <t>建物外構</t>
-        </is>
-      </c>
-      <c r="G45" s="0" t="inlineStr">
-        <is>
-          <t>コンクリート塀・ブロック塀</t>
-        </is>
-      </c>
-      <c r="I45" s="0" t="inlineStr">
-        <is>
-          <t>給水機器</t>
-        </is>
-      </c>
-      <c r="J45" s="0" t="inlineStr">
-        <is>
-          <t>散水栓</t>
-        </is>
-      </c>
-      <c r="L45" s="0" t="inlineStr">
-        <is>
-          <t>レンジ</t>
-        </is>
-      </c>
-      <c r="M45" s="0" t="inlineStr">
-        <is>
-          <t>テーブルレンジ</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="F46" s="0" t="inlineStr">
-        <is>
-          <t>建物外構</t>
-        </is>
-      </c>
-      <c r="G46" s="0" t="inlineStr">
-        <is>
-          <t>舗装・砂利敷</t>
-        </is>
-      </c>
-      <c r="I46" s="0" t="inlineStr">
-        <is>
-          <t>給水機器</t>
-        </is>
-      </c>
-      <c r="J46" s="0" t="inlineStr">
-        <is>
-          <t>弁</t>
-        </is>
-      </c>
-      <c r="L46" s="0" t="inlineStr">
-        <is>
-          <t>レンジ</t>
-        </is>
-      </c>
-      <c r="M46" s="0" t="inlineStr">
-        <is>
-          <t>卓上コンロ</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="F47" s="0" t="inlineStr">
-        <is>
-          <t>建物外構</t>
-        </is>
-      </c>
-      <c r="G47" s="0" t="inlineStr">
-        <is>
-          <t>車止め・縁石・ガードポール</t>
-        </is>
-      </c>
-      <c r="I47" s="0" t="inlineStr">
-        <is>
-          <t>給水機器</t>
-        </is>
-      </c>
-      <c r="J47" s="0" t="inlineStr">
-        <is>
-          <t>その他給水設備</t>
-        </is>
-      </c>
-      <c r="L47" s="0" t="inlineStr">
-        <is>
-          <t>レンジ</t>
-        </is>
-      </c>
-      <c r="M47" s="0" t="inlineStr">
-        <is>
-          <t>ローレンジ</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="F48" s="0" t="inlineStr">
-        <is>
-          <t>建物外構</t>
-        </is>
-      </c>
-      <c r="G48" s="0" t="inlineStr">
-        <is>
-          <t>残地・法面</t>
-        </is>
-      </c>
-      <c r="I48" s="0" t="inlineStr">
-        <is>
-          <t>排水機器</t>
-        </is>
-      </c>
-      <c r="J48" s="0" t="inlineStr">
-        <is>
-          <t>グリーストラップ</t>
-        </is>
-      </c>
-      <c r="L48" s="0" t="inlineStr">
-        <is>
-          <t>レンジ</t>
-        </is>
-      </c>
-      <c r="M48" s="0" t="inlineStr">
-        <is>
-          <t>中華レンジ</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="F49" s="0" t="inlineStr">
-        <is>
-          <t>建物外構</t>
-        </is>
-      </c>
-      <c r="G49" s="0" t="inlineStr">
-        <is>
-          <t>倉庫</t>
-        </is>
-      </c>
-      <c r="I49" s="0" t="inlineStr">
-        <is>
-          <t>排水機器</t>
-        </is>
-      </c>
-      <c r="J49" s="0" t="inlineStr">
-        <is>
-          <t>浄化槽</t>
-        </is>
-      </c>
-      <c r="L49" s="0" t="inlineStr">
-        <is>
-          <t>レンジ</t>
-        </is>
-      </c>
-      <c r="M49" s="0" t="inlineStr">
-        <is>
-          <t>鋳物コンロ</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="F50" s="0" t="inlineStr">
-        <is>
-          <t>建物外構</t>
-        </is>
-      </c>
-      <c r="G50" s="0" t="inlineStr">
-        <is>
-          <t>犬走り</t>
-        </is>
-      </c>
-      <c r="I50" s="0" t="inlineStr">
-        <is>
-          <t>排水機器</t>
-        </is>
-      </c>
-      <c r="J50" s="0" t="inlineStr">
-        <is>
-          <t>ポンプ</t>
-        </is>
-      </c>
-      <c r="L50" s="0" t="inlineStr">
-        <is>
-          <t>煮炊釜</t>
-        </is>
-      </c>
-      <c r="M50" s="0" t="inlineStr">
-        <is>
-          <t>回転釜</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="F51" s="0" t="inlineStr">
-        <is>
-          <t>建物外構</t>
-        </is>
-      </c>
-      <c r="G51" s="0" t="inlineStr">
-        <is>
-          <t>植栽</t>
-        </is>
-      </c>
-      <c r="I51" s="0" t="inlineStr">
-        <is>
-          <t>排水機器</t>
-        </is>
-      </c>
-      <c r="J51" s="0" t="inlineStr">
-        <is>
-          <t>排水溝</t>
-        </is>
-      </c>
-      <c r="L51" s="0" t="inlineStr">
-        <is>
-          <t>煮炊釜</t>
-        </is>
-      </c>
-      <c r="M51" s="0" t="inlineStr">
-        <is>
-          <t>ティルティングパン</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="F52" s="0" t="inlineStr">
-        <is>
-          <t>建物外構</t>
-        </is>
-      </c>
-      <c r="G52" s="0" t="inlineStr">
-        <is>
-          <t>側溝・蓋・枡蓋</t>
-        </is>
-      </c>
-      <c r="I52" s="0" t="inlineStr">
-        <is>
-          <t>排水機器</t>
-        </is>
-      </c>
-      <c r="J52" s="0" t="inlineStr">
-        <is>
-          <t>排水設備</t>
-        </is>
-      </c>
-      <c r="L52" s="0" t="inlineStr">
-        <is>
-          <t>煮炊釜</t>
-        </is>
-      </c>
-      <c r="M52" s="0" t="inlineStr">
-        <is>
-          <t>その他煮炊き釜</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="F53" s="0" t="inlineStr">
-        <is>
-          <t>建物外構</t>
-        </is>
-      </c>
-      <c r="G53" s="0" t="inlineStr">
-        <is>
-          <t>その他建物外</t>
-        </is>
-      </c>
-      <c r="I53" s="0" t="inlineStr">
-        <is>
-          <t>衛生機器</t>
-        </is>
-      </c>
-      <c r="J53" s="0" t="inlineStr">
-        <is>
-          <t>水栓</t>
-        </is>
-      </c>
-      <c r="L53" s="0" t="inlineStr">
-        <is>
-          <t>焼物器</t>
-        </is>
-      </c>
-      <c r="M53" s="0" t="inlineStr">
-        <is>
-          <t>オーブン</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="I54" s="0" t="inlineStr">
-        <is>
-          <t>衛生機器</t>
-        </is>
-      </c>
-      <c r="J54" s="0" t="inlineStr">
-        <is>
-          <t>自動水栓</t>
-        </is>
-      </c>
-      <c r="L54" s="0" t="inlineStr">
-        <is>
-          <t>焼物器</t>
-        </is>
-      </c>
-      <c r="M54" s="0" t="inlineStr">
-        <is>
-          <t>コンベクションオーブン</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="I55" s="0" t="inlineStr">
-        <is>
-          <t>衛生機器</t>
-        </is>
-      </c>
-      <c r="J55" s="0" t="inlineStr">
-        <is>
-          <t>流し台</t>
-        </is>
-      </c>
-      <c r="L55" s="0" t="inlineStr">
-        <is>
-          <t>焼物器</t>
-        </is>
-      </c>
-      <c r="M55" s="0" t="inlineStr">
-        <is>
-          <t>スチームコンベクションオーブン</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="I56" s="0" t="inlineStr">
-        <is>
-          <t>衛生機器</t>
-        </is>
-      </c>
-      <c r="J56" s="0" t="inlineStr">
-        <is>
-          <t>鏡</t>
-        </is>
-      </c>
-      <c r="L56" s="0" t="inlineStr">
-        <is>
-          <t>揚物器</t>
-        </is>
-      </c>
-      <c r="M56" s="0" t="inlineStr">
-        <is>
-          <t>フライヤー</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="I57" s="0" t="inlineStr">
-        <is>
-          <t>衛生機器</t>
-        </is>
-      </c>
-      <c r="J57" s="0" t="inlineStr">
-        <is>
-          <t>水石鹸入れ</t>
-        </is>
-      </c>
-      <c r="L57" s="0" t="inlineStr">
-        <is>
-          <t>揚物器</t>
-        </is>
-      </c>
-      <c r="M57" s="0" t="inlineStr">
-        <is>
-          <t>プレッシャーフライヤー</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="I58" s="0" t="inlineStr">
-        <is>
-          <t>衛生機器</t>
-        </is>
-      </c>
-      <c r="J58" s="0" t="inlineStr">
-        <is>
-          <t>洋式便器</t>
-        </is>
-      </c>
-      <c r="L58" s="0" t="inlineStr">
-        <is>
-          <t>揚物器</t>
-        </is>
-      </c>
-      <c r="M58" s="0" t="inlineStr">
-        <is>
-          <t>連続式フライヤー</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="I59" s="0" t="inlineStr">
-        <is>
-          <t>衛生機器</t>
-        </is>
-      </c>
-      <c r="J59" s="0" t="inlineStr">
-        <is>
-          <t>和式便器</t>
-        </is>
-      </c>
-      <c r="L59" s="0" t="inlineStr">
-        <is>
-          <t>蒸し器</t>
-        </is>
-      </c>
-      <c r="M59" s="0" t="inlineStr">
-        <is>
-          <t>無圧式スチーマー</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="I60" s="0" t="inlineStr">
-        <is>
-          <t>衛生機器</t>
-        </is>
-      </c>
-      <c r="J60" s="0" t="inlineStr">
-        <is>
-          <t>小便器</t>
-        </is>
-      </c>
-      <c r="L60" s="0" t="inlineStr">
-        <is>
-          <t>蒸し器</t>
-        </is>
-      </c>
-      <c r="M60" s="0" t="inlineStr">
-        <is>
-          <t>加圧式スチーマー</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="I61" s="0" t="inlineStr">
-        <is>
-          <t>衛生機器</t>
-        </is>
-      </c>
-      <c r="J61" s="0" t="inlineStr">
-        <is>
-          <t>温水洗浄便座</t>
-        </is>
-      </c>
-      <c r="L61" s="0" t="inlineStr">
-        <is>
-          <t>炊飯器</t>
-        </is>
-      </c>
-      <c r="M61" s="0" t="inlineStr">
-        <is>
-          <t>立体炊飯器</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="I62" s="0" t="inlineStr">
-        <is>
-          <t>衛生機器</t>
-        </is>
-      </c>
-      <c r="J62" s="0" t="inlineStr">
-        <is>
-          <t>暖房便座・便座</t>
-        </is>
-      </c>
-      <c r="L62" s="0" t="inlineStr">
-        <is>
-          <t>炊飯器</t>
-        </is>
-      </c>
-      <c r="M62" s="0" t="inlineStr">
-        <is>
-          <t>連続炊飯装置</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="I63" s="0" t="inlineStr">
-        <is>
-          <t>衛生機器</t>
-        </is>
-      </c>
-      <c r="J63" s="0" t="inlineStr">
-        <is>
-          <t>手洗器・洗濯流し(SK)</t>
-        </is>
-      </c>
-      <c r="L63" s="0" t="inlineStr">
-        <is>
-          <t>食材洗浄機</t>
-        </is>
-      </c>
-      <c r="M63" s="0" t="inlineStr">
-        <is>
-          <t>球根皮むき機</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="I64" s="0" t="inlineStr">
-        <is>
-          <t>衛生機器</t>
-        </is>
-      </c>
-      <c r="J64" s="0" t="inlineStr">
-        <is>
-          <t>ペーパーホルダー</t>
-        </is>
-      </c>
-      <c r="L64" s="0" t="inlineStr">
-        <is>
-          <t>食材洗浄機</t>
-        </is>
-      </c>
-      <c r="M64" s="0" t="inlineStr">
-        <is>
-          <t>野菜洗浄機</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="I65" s="0" t="inlineStr">
-        <is>
-          <t>衛生機器</t>
-        </is>
-      </c>
-      <c r="J65" s="0" t="inlineStr">
-        <is>
-          <t>その他衛生器具</t>
-        </is>
-      </c>
-      <c r="L65" s="0" t="inlineStr">
-        <is>
-          <t>食材洗浄機</t>
-        </is>
-      </c>
-      <c r="M65" s="0" t="inlineStr">
-        <is>
-          <t>脱水機</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="I66" s="0" t="inlineStr">
-        <is>
-          <t>給湯機器</t>
-        </is>
-      </c>
-      <c r="J66" s="0" t="inlineStr">
-        <is>
-          <t>湯沸器</t>
-        </is>
-      </c>
-      <c r="L66" s="0" t="inlineStr">
-        <is>
-          <t>食材洗浄機</t>
-        </is>
-      </c>
-      <c r="M66" s="0" t="inlineStr">
-        <is>
-          <t>水圧式洗米機</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="I67" s="0" t="inlineStr">
-        <is>
-          <t>給湯機器</t>
-        </is>
-      </c>
-      <c r="J67" s="0" t="inlineStr">
-        <is>
-          <t>ポンプ</t>
-        </is>
-      </c>
-      <c r="L67" s="0" t="inlineStr">
-        <is>
-          <t>食材洗浄機</t>
-        </is>
-      </c>
-      <c r="M67" s="0" t="inlineStr">
-        <is>
-          <t>連続洗米機</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="I68" s="0" t="inlineStr">
-        <is>
-          <t>蒸気設備</t>
-        </is>
-      </c>
-      <c r="J68" s="0" t="inlineStr">
-        <is>
-          <t>蒸気ボイラー</t>
-        </is>
-      </c>
-      <c r="L68" s="0" t="inlineStr">
-        <is>
-          <t>食材洗浄機</t>
-        </is>
-      </c>
-      <c r="M68" s="0" t="inlineStr">
-        <is>
-          <t>自動計量洗米機</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="I69" s="0" t="inlineStr">
-        <is>
-          <t>蒸気設備</t>
-        </is>
-      </c>
-      <c r="J69" s="0" t="inlineStr">
-        <is>
-          <t>減圧弁</t>
-        </is>
-      </c>
-      <c r="L69" s="0" t="inlineStr">
-        <is>
-          <t>切裁機</t>
-        </is>
-      </c>
-      <c r="M69" s="0" t="inlineStr">
-        <is>
-          <t>野菜切裁機</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="I70" s="0" t="inlineStr">
-        <is>
-          <t>蒸気設備</t>
-        </is>
-      </c>
-      <c r="J70" s="0" t="inlineStr">
-        <is>
-          <t>安全装置</t>
-        </is>
-      </c>
-      <c r="L70" s="0" t="inlineStr">
-        <is>
-          <t>切裁機</t>
-        </is>
-      </c>
-      <c r="M70" s="0" t="inlineStr">
-        <is>
-          <t>フードスライサー</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="I71" s="0" t="inlineStr">
-        <is>
-          <t>ダクトおよび配管</t>
-        </is>
-      </c>
-      <c r="J71" s="0" t="inlineStr">
-        <is>
-          <t>空調ダクト</t>
-        </is>
-      </c>
-      <c r="L71" s="0" t="inlineStr">
-        <is>
-          <t>切裁機</t>
-        </is>
-      </c>
-      <c r="M71" s="0" t="inlineStr">
-        <is>
-          <t>さいの目切り機</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="I72" s="0" t="inlineStr">
-        <is>
-          <t>ダクトおよび配管</t>
-        </is>
-      </c>
-      <c r="J72" s="0" t="inlineStr">
-        <is>
-          <t>換気ダクト</t>
-        </is>
-      </c>
-      <c r="L72" s="0" t="inlineStr">
-        <is>
-          <t>切裁機</t>
-        </is>
-      </c>
-      <c r="M72" s="0" t="inlineStr">
-        <is>
-          <t>せん切り機</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="I73" s="0" t="inlineStr">
-        <is>
-          <t>ダクトおよび配管</t>
-        </is>
-      </c>
-      <c r="J73" s="0" t="inlineStr">
-        <is>
-          <t>給水管</t>
-        </is>
-      </c>
-      <c r="L73" s="0" t="inlineStr">
-        <is>
-          <t>切裁機</t>
-        </is>
-      </c>
-      <c r="M73" s="0" t="inlineStr">
-        <is>
-          <t>フードカッター</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="I74" s="0" t="inlineStr">
-        <is>
-          <t>ダクトおよび配管</t>
-        </is>
-      </c>
-      <c r="J74" s="0" t="inlineStr">
-        <is>
-          <t>排水管</t>
-        </is>
-      </c>
-      <c r="L74" s="0" t="inlineStr">
-        <is>
-          <t>切裁機</t>
-        </is>
-      </c>
-      <c r="M74" s="0" t="inlineStr">
-        <is>
-          <t>カッターミキサー</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="I75" s="0" t="inlineStr">
-        <is>
-          <t>ダクトおよび配管</t>
-        </is>
-      </c>
-      <c r="J75" s="0" t="inlineStr">
-        <is>
-          <t>蒸気配管</t>
-        </is>
-      </c>
-      <c r="L75" s="0" t="inlineStr">
-        <is>
-          <t>切裁機</t>
-        </is>
-      </c>
-      <c r="M75" s="0" t="inlineStr">
-        <is>
-          <t>その他の切裁機</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="I76" s="0" t="inlineStr">
-        <is>
-          <t>消火設備</t>
-        </is>
-      </c>
-      <c r="J76" s="0" t="inlineStr">
-        <is>
-          <t>消防設備</t>
-        </is>
-      </c>
-      <c r="L76" s="0" t="inlineStr">
-        <is>
-          <t>かくはん混合機</t>
-        </is>
-      </c>
-      <c r="M76" s="0" t="inlineStr">
-        <is>
-          <t>立型フードミキサー</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="I77" s="0" t="inlineStr">
-        <is>
-          <t>消火設備</t>
-        </is>
-      </c>
-      <c r="J77" s="0" t="inlineStr">
-        <is>
-          <t>ポンプ</t>
-        </is>
-      </c>
-      <c r="L77" s="0" t="inlineStr">
-        <is>
-          <t>かくはん混合機</t>
-        </is>
-      </c>
-      <c r="M77" s="0" t="inlineStr">
-        <is>
-          <t>横型フードミキサー</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="I78" s="0" t="inlineStr">
-        <is>
-          <t>消火設備</t>
-        </is>
-      </c>
-      <c r="J78" s="0" t="inlineStr">
-        <is>
-          <t>その他消火設備</t>
-        </is>
-      </c>
-      <c r="L78" s="0" t="inlineStr">
-        <is>
-          <t>かくはん混合機</t>
-        </is>
-      </c>
-      <c r="M78" s="0" t="inlineStr">
-        <is>
-          <t>ブレンダー</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="I79" s="0" t="inlineStr">
-        <is>
-          <t>消火設備</t>
-        </is>
-      </c>
-      <c r="J79" s="0" t="inlineStr">
-        <is>
-          <t>防火扉</t>
-        </is>
-      </c>
-      <c r="L79" s="0" t="inlineStr">
-        <is>
-          <t>かくはん混合機</t>
-        </is>
-      </c>
-      <c r="M79" s="0" t="inlineStr">
-        <is>
-          <t>高速度ミキサー</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="I80" s="0" t="inlineStr">
-        <is>
-          <t>消火設備</t>
-        </is>
-      </c>
-      <c r="J80" s="0" t="inlineStr">
-        <is>
-          <t>防火シャッター</t>
-        </is>
-      </c>
-      <c r="L80" s="0" t="inlineStr">
-        <is>
-          <t>かくはん混合機</t>
-        </is>
-      </c>
-      <c r="M80" s="0" t="inlineStr">
-        <is>
-          <t>その他のミキサー</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="I81" s="0" t="inlineStr">
-        <is>
-          <t>消火設備</t>
-        </is>
-      </c>
-      <c r="J81" s="0" t="inlineStr">
-        <is>
-          <t>防火ダンパー</t>
-        </is>
-      </c>
-      <c r="L81" s="0" t="inlineStr">
-        <is>
-          <t>食品成型機</t>
-        </is>
-      </c>
-      <c r="M81" s="0" t="inlineStr">
-        <is>
-          <t>食品成型機</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="I82" s="0" t="inlineStr">
-        <is>
-          <t>消火設備</t>
-        </is>
-      </c>
-      <c r="J82" s="0" t="inlineStr">
-        <is>
-          <t>防火クロススクリーン</t>
-        </is>
-      </c>
-      <c r="L82" s="0" t="inlineStr">
-        <is>
-          <t>食品成型機</t>
-        </is>
-      </c>
-      <c r="M82" s="0" t="inlineStr">
-        <is>
-          <t>粉付け機</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="I83" s="0" t="inlineStr">
-        <is>
-          <t>消火設備</t>
-        </is>
-      </c>
-      <c r="J83" s="0" t="inlineStr">
-        <is>
-          <t>ドレンチャー</t>
-        </is>
-      </c>
-      <c r="L83" s="0" t="inlineStr">
-        <is>
-          <t>低温貯蔵保管機器</t>
-        </is>
-      </c>
-      <c r="M83" s="0" t="inlineStr">
-        <is>
-          <t>プレハブ式</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="I84" s="0" t="inlineStr">
-        <is>
-          <t>消火設備</t>
-        </is>
-      </c>
-      <c r="J84" s="0" t="inlineStr">
-        <is>
-          <t>その他防火設備</t>
-        </is>
-      </c>
-      <c r="L84" s="0" t="inlineStr">
-        <is>
-          <t>低温貯蔵保管機器</t>
-        </is>
-      </c>
-      <c r="M84" s="0" t="inlineStr">
-        <is>
-          <t>リーチイン式</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="I85" s="0" t="inlineStr">
-        <is>
-          <t>排煙設備</t>
-        </is>
-      </c>
-      <c r="J85" s="0" t="inlineStr">
-        <is>
-          <t>排煙ファン</t>
-        </is>
-      </c>
-      <c r="L85" s="0" t="inlineStr">
-        <is>
-          <t>低温貯蔵保管機器</t>
-        </is>
-      </c>
-      <c r="M85" s="0" t="inlineStr">
-        <is>
-          <t>⽜乳保冷庫</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="I86" s="0" t="inlineStr">
-        <is>
-          <t>排煙設備</t>
-        </is>
-      </c>
-      <c r="J86" s="0" t="inlineStr">
-        <is>
-          <t>排煙口</t>
-        </is>
-      </c>
-      <c r="L86" s="0" t="inlineStr">
-        <is>
-          <t>鮮度向上生産機器</t>
-        </is>
-      </c>
-      <c r="M86" s="0" t="inlineStr">
-        <is>
-          <t>急速冷凍庫</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="I87" s="0" t="inlineStr">
-        <is>
-          <t>排煙設備</t>
-        </is>
-      </c>
-      <c r="J87" s="0" t="inlineStr">
-        <is>
-          <t>その他排煙設備</t>
-        </is>
-      </c>
-      <c r="L87" s="0" t="inlineStr">
-        <is>
-          <t>鮮度向上生産機器</t>
-        </is>
-      </c>
-      <c r="M87" s="0" t="inlineStr">
-        <is>
-          <t>ブラストチラー</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="I88" s="0" t="inlineStr">
-        <is>
-          <t>防煙設備</t>
-        </is>
-      </c>
-      <c r="J88" s="0" t="inlineStr">
-        <is>
-          <t>防煙壁</t>
-        </is>
-      </c>
-      <c r="L88" s="0" t="inlineStr">
-        <is>
-          <t>鮮度向上生産機器</t>
-        </is>
-      </c>
-      <c r="M88" s="0" t="inlineStr">
-        <is>
-          <t>真空冷却機</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="I89" s="0" t="inlineStr">
-        <is>
-          <t>防煙設備</t>
-        </is>
-      </c>
-      <c r="J89" s="0" t="inlineStr">
-        <is>
-          <t>その他防煙設備</t>
-        </is>
-      </c>
-      <c r="L89" s="0" t="inlineStr">
-        <is>
-          <t>低温物流機器</t>
-        </is>
-      </c>
-      <c r="M89" s="0" t="inlineStr">
-        <is>
-          <t>コールドロールボックス</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="I90" s="0" t="inlineStr">
-        <is>
-          <t>誘導設備</t>
-        </is>
-      </c>
-      <c r="J90" s="0" t="inlineStr">
-        <is>
-          <t>非常用照明装置</t>
-        </is>
-      </c>
-      <c r="L90" s="0" t="inlineStr">
-        <is>
-          <t>食器洗浄機</t>
-        </is>
-      </c>
-      <c r="M90" s="0" t="inlineStr">
-        <is>
-          <t>ドアタイプ洗浄機</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="I91" s="0" t="inlineStr">
-        <is>
-          <t>誘導設備</t>
-        </is>
-      </c>
-      <c r="J91" s="0" t="inlineStr">
-        <is>
-          <t>誘導灯</t>
-        </is>
-      </c>
-      <c r="L91" s="0" t="inlineStr">
-        <is>
-          <t>食器洗浄機</t>
-        </is>
-      </c>
-      <c r="M91" s="0" t="inlineStr">
-        <is>
-          <t>アンダーカウンタタイプ洗浄機</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="I92" s="0" t="inlineStr">
-        <is>
-          <t>搬送設備</t>
-        </is>
-      </c>
-      <c r="J92" s="0" t="inlineStr">
-        <is>
-          <t>コンベア</t>
-        </is>
-      </c>
-      <c r="L92" s="0" t="inlineStr">
-        <is>
-          <t>食器洗浄機</t>
-        </is>
-      </c>
-      <c r="M92" s="0" t="inlineStr">
-        <is>
-          <t>フードタイプ洗浄機</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="I93" s="0" t="inlineStr">
-        <is>
-          <t>搬送設備</t>
-        </is>
-      </c>
-      <c r="J93" s="0" t="inlineStr">
-        <is>
-          <t>米サイロ</t>
-        </is>
-      </c>
-      <c r="L93" s="0" t="inlineStr">
-        <is>
-          <t>食器洗浄機</t>
-        </is>
-      </c>
-      <c r="M93" s="0" t="inlineStr">
-        <is>
-          <t>コンベアタイプ洗浄機</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="I94" s="0" t="inlineStr">
-        <is>
-          <t>搬送設備</t>
-        </is>
-      </c>
-      <c r="J94" s="0" t="inlineStr">
-        <is>
-          <t>昇降機</t>
-        </is>
-      </c>
-      <c r="L94" s="0" t="inlineStr">
-        <is>
-          <t>食器洗浄機</t>
-        </is>
-      </c>
-      <c r="M94" s="0" t="inlineStr">
-        <is>
-          <t>かき上げタイプ洗浄機</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="I95" s="0" t="inlineStr">
-        <is>
-          <t>共用機器</t>
-        </is>
-      </c>
-      <c r="J95" s="0" t="inlineStr">
-        <is>
-          <t>シンク</t>
-        </is>
-      </c>
-      <c r="L95" s="0" t="inlineStr">
-        <is>
-          <t>食器洗浄機</t>
-        </is>
-      </c>
-      <c r="M95" s="0" t="inlineStr">
-        <is>
-          <t>ラウンドタイプ洗浄機</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="I96" s="0" t="inlineStr">
-        <is>
-          <t>共用機器</t>
-        </is>
-      </c>
-      <c r="J96" s="0" t="inlineStr">
-        <is>
-          <t>厨房用台類</t>
-        </is>
-      </c>
-      <c r="L96" s="0" t="inlineStr">
-        <is>
-          <t>食器洗浄機</t>
-        </is>
-      </c>
-      <c r="M96" s="0" t="inlineStr">
-        <is>
-          <t>超音波洗浄機</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="I97" s="0" t="inlineStr">
-        <is>
-          <t>共用機器</t>
-        </is>
-      </c>
-      <c r="J97" s="0" t="inlineStr">
-        <is>
-          <t>厨房用棚類</t>
-        </is>
-      </c>
-      <c r="L97" s="0" t="inlineStr">
-        <is>
-          <t>食器洗浄機</t>
-        </is>
-      </c>
-      <c r="M97" s="0" t="inlineStr">
-        <is>
-          <t>その他の食器洗浄機</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="I98" s="0" t="inlineStr">
-        <is>
-          <t>熱調理機器</t>
-        </is>
-      </c>
-      <c r="J98" s="0" t="inlineStr">
-        <is>
-          <t>レンジ</t>
-        </is>
-      </c>
-      <c r="L98" s="0" t="inlineStr">
-        <is>
-          <t>消毒機器</t>
-        </is>
-      </c>
-      <c r="M98" s="0" t="inlineStr">
-        <is>
-          <t>棚式消毒保管庫</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="I99" s="0" t="inlineStr">
-        <is>
-          <t>熱調理機器</t>
-        </is>
-      </c>
-      <c r="J99" s="0" t="inlineStr">
-        <is>
-          <t>煮炊釜</t>
-        </is>
-      </c>
-      <c r="L99" s="0" t="inlineStr">
-        <is>
-          <t>消毒機器</t>
-        </is>
-      </c>
-      <c r="M99" s="0" t="inlineStr">
-        <is>
-          <t>カートイン式消毒保管庫</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="I100" s="0" t="inlineStr">
-        <is>
-          <t>熱調理機器</t>
-        </is>
-      </c>
-      <c r="J100" s="0" t="inlineStr">
-        <is>
-          <t>焼物器</t>
-        </is>
-      </c>
-      <c r="L100" s="0" t="inlineStr">
-        <is>
-          <t>消毒機器</t>
-        </is>
-      </c>
-      <c r="M100" s="0" t="inlineStr">
-        <is>
-          <t>天吊り式消毒装置</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="I101" s="0" t="inlineStr">
-        <is>
-          <t>熱調理機器</t>
-        </is>
-      </c>
-      <c r="J101" s="0" t="inlineStr">
-        <is>
-          <t>揚物器</t>
-        </is>
-      </c>
-      <c r="L101" s="0" t="inlineStr">
-        <is>
-          <t>保温機器</t>
-        </is>
-      </c>
-      <c r="M101" s="0" t="inlineStr">
-        <is>
-          <t>ウオーマーテーブル</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="I102" s="0" t="inlineStr">
-        <is>
-          <t>熱調理機器</t>
-        </is>
-      </c>
-      <c r="J102" s="0" t="inlineStr">
-        <is>
-          <t>蒸し器</t>
-        </is>
-      </c>
-      <c r="L102" s="0" t="inlineStr">
-        <is>
-          <t>保温機器</t>
-        </is>
-      </c>
-      <c r="M102" s="0" t="inlineStr">
-        <is>
-          <t>温蔵庫</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="I103" s="0" t="inlineStr">
-        <is>
-          <t>熱調理機器</t>
-        </is>
-      </c>
-      <c r="J103" s="0" t="inlineStr">
-        <is>
-          <t>炊飯器</t>
-        </is>
-      </c>
-      <c r="L103" s="0" t="inlineStr">
-        <is>
-          <t>保温機器</t>
-        </is>
-      </c>
-      <c r="M103" s="0" t="inlineStr">
-        <is>
-          <t>その他の保温機器</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="I104" s="0" t="inlineStr">
-        <is>
-          <t>熱調理機器</t>
-        </is>
-      </c>
-      <c r="J104" s="0" t="inlineStr">
-        <is>
-          <t>その他の熱調理機</t>
-        </is>
-      </c>
-      <c r="L104" s="0" t="inlineStr">
-        <is>
-          <t>ベーカリー関連機器</t>
-        </is>
-      </c>
-      <c r="M104" s="0" t="inlineStr">
-        <is>
-          <t>ドーナツフライヤー</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="I105" s="0" t="inlineStr">
-        <is>
-          <t>下調理機</t>
-        </is>
-      </c>
-      <c r="J105" s="0" t="inlineStr">
-        <is>
-          <t>食材洗浄機</t>
-        </is>
-      </c>
-      <c r="L105" s="0" t="inlineStr">
-        <is>
-          <t>ベーカリー関連機器</t>
-        </is>
-      </c>
-      <c r="M105" s="0" t="inlineStr">
-        <is>
-          <t>ホイロ</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="I106" s="0" t="inlineStr">
-        <is>
-          <t>下調理機</t>
-        </is>
-      </c>
-      <c r="J106" s="0" t="inlineStr">
-        <is>
-          <t>切裁機</t>
-        </is>
-      </c>
-      <c r="L106" s="0" t="inlineStr">
-        <is>
-          <t>ベーカリー関連機器</t>
-        </is>
-      </c>
-      <c r="M106" s="0" t="inlineStr">
-        <is>
-          <t>ドゥコンディショナー</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="I107" s="0" t="inlineStr">
-        <is>
-          <t>下調理機</t>
-        </is>
-      </c>
-      <c r="J107" s="0" t="inlineStr">
-        <is>
-          <t>かくはん混合機</t>
-        </is>
-      </c>
-      <c r="L107" s="0" t="inlineStr">
-        <is>
-          <t>ベーカリー関連機器</t>
-        </is>
-      </c>
-      <c r="M107" s="0" t="inlineStr">
-        <is>
-          <t>解凍庫</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="I108" s="0" t="inlineStr">
-        <is>
-          <t>下調理機</t>
-        </is>
-      </c>
-      <c r="J108" s="0" t="inlineStr">
-        <is>
-          <t>食品成型機</t>
-        </is>
-      </c>
-      <c r="L108" s="0" t="inlineStr">
-        <is>
-          <t>ベーカリー関連機器</t>
-        </is>
-      </c>
-      <c r="M108" s="0" t="inlineStr">
-        <is>
-          <t>ラックカート</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="I109" s="0" t="inlineStr">
-        <is>
-          <t>下調理機</t>
-        </is>
-      </c>
-      <c r="J109" s="0" t="inlineStr">
-        <is>
-          <t>その他の下調理機</t>
-        </is>
-      </c>
-      <c r="L109" s="0" t="inlineStr">
-        <is>
-          <t>ベーカリー関連機器</t>
-        </is>
-      </c>
-      <c r="M109" s="0" t="inlineStr">
-        <is>
-          <t>トンボラック</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="I110" s="0" t="inlineStr">
-        <is>
-          <t>冷却と冷凍・冷蔵設備機器</t>
-        </is>
-      </c>
-      <c r="J110" s="0" t="inlineStr">
-        <is>
-          <t>低温貯蔵保管機器</t>
-        </is>
-      </c>
-      <c r="L110" s="0" t="inlineStr">
-        <is>
-          <t>ベーカリー関連機器</t>
-        </is>
-      </c>
-      <c r="M110" s="0" t="inlineStr">
-        <is>
-          <t>スパイラルミキサー</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="I111" s="0" t="inlineStr">
-        <is>
-          <t>冷却と冷凍・冷蔵設備機器</t>
-        </is>
-      </c>
-      <c r="J111" s="0" t="inlineStr">
-        <is>
-          <t>鮮度向上生産機器</t>
-        </is>
-      </c>
-      <c r="L111" s="0" t="inlineStr">
-        <is>
-          <t>ベーカリー関連機器</t>
-        </is>
-      </c>
-      <c r="M111" s="0" t="inlineStr">
-        <is>
-          <t>成形機</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="I112" s="0" t="inlineStr">
-        <is>
-          <t>冷却と冷凍・冷蔵設備機器</t>
-        </is>
-      </c>
-      <c r="J112" s="0" t="inlineStr">
-        <is>
-          <t>低温物流機器</t>
-        </is>
-      </c>
-      <c r="L112" s="0" t="inlineStr">
-        <is>
-          <t>ベーカリー関連機器</t>
-        </is>
-      </c>
-      <c r="M112" s="0" t="inlineStr">
-        <is>
-          <t>分割丸目機</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="I113" s="0" t="inlineStr">
-        <is>
-          <t>冷却と冷凍・冷蔵設備機器</t>
-        </is>
-      </c>
-      <c r="J113" s="0" t="inlineStr">
-        <is>
-          <t>解凍機器</t>
-        </is>
-      </c>
-      <c r="L113" s="0" t="inlineStr">
-        <is>
-          <t>ベーカリー関連機器</t>
-        </is>
-      </c>
-      <c r="M113" s="0" t="inlineStr">
-        <is>
-          <t>リバースシート</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="I114" s="0" t="inlineStr">
-        <is>
-          <t>冷却と冷凍・冷蔵設備機器</t>
-        </is>
-      </c>
-      <c r="J114" s="0" t="inlineStr">
-        <is>
-          <t>製氷機</t>
-        </is>
-      </c>
-      <c r="L114" s="0" t="inlineStr">
-        <is>
-          <t>ベーカリー関連機器</t>
-        </is>
-      </c>
-      <c r="M114" s="0" t="inlineStr">
-        <is>
-          <t>パンスライサー</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="I115" s="0" t="inlineStr">
-        <is>
-          <t>冷却と冷凍・冷蔵設備機器</t>
-        </is>
-      </c>
-      <c r="J115" s="0" t="inlineStr">
-        <is>
-          <t>その他の冷却冷凍冷蔵設備</t>
-        </is>
-      </c>
-      <c r="L115" s="0" t="inlineStr">
-        <is>
-          <t>ベーカリー関連機器</t>
-        </is>
-      </c>
-      <c r="M115" s="0" t="inlineStr">
-        <is>
-          <t>冷温水水量計</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="I116" s="0" t="inlineStr">
-        <is>
-          <t>食器洗浄機・消毒機器</t>
-        </is>
-      </c>
-      <c r="J116" s="0" t="inlineStr">
-        <is>
-          <t>食器洗浄機</t>
-        </is>
-      </c>
-      <c r="L116" s="0" t="inlineStr">
+      <c r="L150" t="inlineStr">
         <is>
           <t>配膳車・下膳車</t>
         </is>
       </c>
-      <c r="M116" s="0" t="inlineStr">
-        <is>
-          <t>コンテナ</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="I117" s="0" t="inlineStr">
-        <is>
-          <t>食器洗浄機・消毒機器</t>
-        </is>
-      </c>
-      <c r="J117" s="0" t="inlineStr">
-        <is>
-          <t>消毒機器</t>
-        </is>
-      </c>
-      <c r="L117" s="0" t="inlineStr">
+      <c r="M150" t="inlineStr">
+        <is>
+          <t>冷温蔵配膳車</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="L151" t="inlineStr">
         <is>
           <t>配膳車・下膳車</t>
         </is>
       </c>
-      <c r="M117" s="0" t="inlineStr">
-        <is>
-          <t>冷温蔵配膳車</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="I118" s="0" t="inlineStr">
-        <is>
-          <t>サービス機器</t>
-        </is>
-      </c>
-      <c r="J118" s="0" t="inlineStr">
-        <is>
-          <t>保温機器</t>
-        </is>
-      </c>
-      <c r="L118" s="0" t="inlineStr">
+      <c r="M151" t="inlineStr">
+        <is>
+          <t>常温配膳車</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="L152" t="inlineStr">
         <is>
           <t>配膳車・下膳車</t>
         </is>
       </c>
-      <c r="M118" s="0" t="inlineStr">
-        <is>
-          <t>常温配膳車</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="I119" s="0" t="inlineStr">
-        <is>
-          <t>サービス機器</t>
-        </is>
-      </c>
-      <c r="J119" s="0" t="inlineStr">
-        <is>
-          <t>ベーカリー関連機器</t>
-        </is>
-      </c>
-      <c r="L119" s="0" t="inlineStr">
-        <is>
-          <t>配膳車・下膳車</t>
-        </is>
-      </c>
-      <c r="M119" s="0" t="inlineStr">
+      <c r="M152" t="inlineStr">
         <is>
           <t>下膳車</t>
         </is>
       </c>
     </row>
-    <row r="120">
-      <c r="I120" s="0" t="inlineStr">
-        <is>
-          <t>サービス機器</t>
-        </is>
-      </c>
-      <c r="J120" s="0" t="inlineStr">
-        <is>
-          <t>配膳車・下膳車</t>
-        </is>
-      </c>
-      <c r="L120" s="0" t="inlineStr">
+    <row r="153">
+      <c r="L153" t="inlineStr">
         <is>
           <t>生ごみ処理</t>
         </is>
       </c>
-      <c r="M120" s="0" t="inlineStr">
+      <c r="M153" t="inlineStr">
         <is>
           <t>厨芥処理システム</t>
         </is>
       </c>
     </row>
-    <row r="121">
-      <c r="I121" s="0" t="inlineStr">
-        <is>
-          <t>食品廃棄物など処理機器</t>
-        </is>
-      </c>
-      <c r="J121" s="0" t="inlineStr">
+    <row r="154">
+      <c r="L154" t="inlineStr">
         <is>
           <t>生ごみ処理</t>
         </is>
       </c>
-      <c r="L121" s="0" t="inlineStr">
+      <c r="M154" t="inlineStr">
+        <is>
+          <t>ディスポーザー</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="L155" t="inlineStr">
         <is>
           <t>生ごみ処理</t>
         </is>
       </c>
-      <c r="M121" s="0" t="inlineStr">
-        <is>
-          <t>ディスポーザー</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="I122" s="0" t="inlineStr">
-        <is>
-          <t>食品廃棄物など処理機器</t>
-        </is>
-      </c>
-      <c r="J122" s="0" t="inlineStr">
-        <is>
-          <t>コンパクター</t>
-        </is>
-      </c>
-      <c r="L122" s="0" t="inlineStr">
-        <is>
-          <t>生ごみ処理</t>
-        </is>
-      </c>
-      <c r="M122" s="0" t="inlineStr">
+      <c r="M155" t="inlineStr">
         <is>
           <t>生ごみ処理機</t>
         </is>
       </c>
     </row>
-    <row r="123">
-      <c r="I123" s="0" t="inlineStr">
-        <is>
-          <t>食品廃棄物など処理機器</t>
-        </is>
-      </c>
-      <c r="J123" s="0" t="inlineStr">
-        <is>
-          <t>パルパーエストラシステム</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="I124" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">配管設備 </t>
-        </is>
-      </c>
-      <c r="J124" s="0" t="inlineStr">
-        <is>
-          <t>ガス栓</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="I125" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">配管設備 </t>
-        </is>
-      </c>
-      <c r="J125" s="0" t="inlineStr">
-        <is>
-          <t>ガス接続具</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="I126" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">配管設備 </t>
-        </is>
-      </c>
-      <c r="J126" s="0" t="inlineStr">
-        <is>
-          <t>ガス漏れ警報器等</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="I127" s="0" t="inlineStr">
-        <is>
-          <t>給湯室等設備</t>
-        </is>
-      </c>
-      <c r="J127" s="0" t="inlineStr">
-        <is>
-          <t>ガス器具</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="I128" s="0" t="inlineStr">
-        <is>
-          <t>観測対象</t>
-        </is>
-      </c>
-      <c r="J128" s="0" t="inlineStr">
-        <is>
-          <t>空間</t>
-        </is>
-      </c>
-    </row>
-    <row r="129">
-      <c r="I129" s="0" t="inlineStr">
-        <is>
-          <t>観測対象</t>
-        </is>
-      </c>
-      <c r="J129" s="0" t="inlineStr">
-        <is>
-          <t>水</t>
-        </is>
-      </c>
-    </row>
-    <row r="130">
-      <c r="I130" s="0" t="inlineStr">
-        <is>
-          <t>観測対象</t>
-        </is>
-      </c>
-      <c r="J130" s="0" t="inlineStr">
-        <is>
-          <t>蒸気</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="I131" s="0" t="inlineStr">
-        <is>
-          <t>センサー</t>
-        </is>
-      </c>
-      <c r="J131" s="0" t="inlineStr">
-        <is>
-          <t>センサー</t>
-        </is>
-      </c>
-    </row>
-    <row r="132">
-      <c r="I132" s="0" t="inlineStr">
-        <is>
-          <t>プール</t>
-        </is>
-      </c>
-      <c r="J132" s="0" t="inlineStr">
-        <is>
-          <t>プール</t>
-        </is>
-      </c>
-    </row>
-    <row r="133">
-      <c r="I133" s="0" t="inlineStr">
-        <is>
-          <t>プール</t>
-        </is>
-      </c>
-      <c r="J133" s="0" t="inlineStr">
-        <is>
-          <t>プール設備</t>
-        </is>
-      </c>
-    </row>
-    <row r="134">
-      <c r="I134" s="0" t="inlineStr">
-        <is>
-          <t>水槽</t>
-        </is>
-      </c>
-      <c r="J134" s="0" t="inlineStr">
-        <is>
-          <t>水槽</t>
-        </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="I135" s="0" t="inlineStr">
-        <is>
-          <t>舞台装置</t>
-        </is>
-      </c>
-      <c r="J135" s="0" t="inlineStr">
-        <is>
-          <t>舞台機構</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="I136" s="0" t="inlineStr">
-        <is>
-          <t>舞台装置</t>
-        </is>
-      </c>
-      <c r="J136" s="0" t="inlineStr">
-        <is>
-          <t>舞台照明</t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="I137" s="0" t="inlineStr">
-        <is>
-          <t>舞台装置</t>
-        </is>
-      </c>
-      <c r="J137" s="0" t="inlineStr">
-        <is>
-          <t>舞台音響</t>
-        </is>
-      </c>
-    </row>
-    <row r="138">
-      <c r="I138" s="0" t="inlineStr">
-        <is>
-          <t>舞台装置</t>
-        </is>
-      </c>
-      <c r="J138" s="0" t="inlineStr">
-        <is>
-          <t>舞台装置</t>
-        </is>
-      </c>
-    </row>
-    <row r="139">
-      <c r="I139" s="0" t="inlineStr">
-        <is>
-          <t>遊具</t>
-        </is>
-      </c>
-      <c r="J139" s="0" t="inlineStr">
-        <is>
-          <t>遊具</t>
-        </is>
-      </c>
-    </row>
-    <row r="140">
-      <c r="I140" s="0" t="inlineStr">
-        <is>
-          <t>植栽</t>
-        </is>
-      </c>
-      <c r="J140" s="0" t="inlineStr">
-        <is>
-          <t>植栽</t>
-        </is>
-      </c>
-    </row>
-    <row r="141">
-      <c r="I141" s="0" t="inlineStr">
-        <is>
-          <t>その他設備</t>
-        </is>
-      </c>
-      <c r="J141" s="0" t="inlineStr">
-        <is>
-          <t>椅子</t>
-        </is>
-      </c>
-    </row>
-    <row r="142">
-      <c r="I142" s="0" t="inlineStr">
-        <is>
-          <t>その他設備</t>
-        </is>
-      </c>
-      <c r="J142" s="0" t="inlineStr">
-        <is>
-          <t>その他設備</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <mergeCells count="5">
-    <mergeCell ref="C1:D1"/>
-    <mergeCell ref="L1:M1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="I1:J1"/>
-    <mergeCell ref="A1:A2"/>
-  </mergeCells>
   <pageMargins left="0.2362204724409449" right="0.2362204724409449" top="0.7480314960629921" bottom="0.7480314960629921" header="0.3149606299212598" footer="0.3149606299212598"/>
   <pageSetup orientation="landscape" paperSize="9" scale="64" fitToHeight="0"/>
 </worksheet>
@@ -4912,135 +5361,225 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A18"/>
+  <dimension ref="A1:B18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="12"/>
   <cols>
     <col width="41.28515625" customWidth="1" style="9" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="0" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>天災(豪雨・落雷等)</t>
         </is>
       </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>天災に起因。津波・洪水・越水・暴風・落雷など。但し、地震の揺れや地割れが直接的原因となる場合を除く。</t>
+        </is>
+      </c>
     </row>
     <row r="2">
-      <c r="A2" s="0" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>地震</t>
         </is>
       </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>地震による揺れや地割れに起因。但し、地震による津波や火災は“天災”に分類。</t>
+        </is>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="0" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>物落下・衝突(不意のもの)</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>外部から物体が衝突したことに起因。但し、車両事故を除く。</t>
+        </is>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" s="0" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>車輌事故</t>
         </is>
       </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>車両が衝突するなどの車両事故に起因。</t>
+        </is>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" s="0" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>近隣・施設利用者クレーム(騒音・危険性)</t>
         </is>
       </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>特に故障などの異常が無いが、何らかの不具合が指摘された。Phenomenonが“改善提案”に対応する列挙型メンバ。</t>
+        </is>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="0" t="inlineStr">
+      <c r="A6" t="inlineStr">
         <is>
           <t>原因不明</t>
         </is>
       </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>原因が特定できない。</t>
+        </is>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="0" t="inlineStr">
+      <c r="A7" t="inlineStr">
         <is>
           <t>機器故障</t>
         </is>
       </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>不具合が発生した対象物以外の機器の故障が影響。</t>
+        </is>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" s="0" t="inlineStr">
+      <c r="A8" t="inlineStr">
         <is>
           <t>盗難・いたずら(故意)</t>
         </is>
       </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>盗難やいたずらなどの故意の行為に起因。落書きを除く。</t>
+        </is>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" s="0" t="inlineStr">
+      <c r="A9" t="inlineStr">
         <is>
           <t>施工・メーカ瑕疵</t>
         </is>
       </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>機器や部材のメーカや施工者の瑕疵に起因。</t>
+        </is>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" s="0" t="inlineStr">
+      <c r="A10" t="inlineStr">
         <is>
           <t>経年劣化</t>
         </is>
       </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>長期間正常に使用したことに起因。</t>
+        </is>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" s="0" t="inlineStr">
+      <c r="A11" t="inlineStr">
         <is>
           <t>性能・耐久不足</t>
         </is>
       </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>元々設備や部材の能力が負荷に対して低い。</t>
+        </is>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" s="0" t="inlineStr">
+      <c r="A12" t="inlineStr">
         <is>
           <t>建物立地</t>
         </is>
       </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>他の項目以外の立地に起因した不具合。</t>
+        </is>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" s="0" t="inlineStr">
+      <c r="A13" t="inlineStr">
         <is>
           <t>地盤沈下</t>
         </is>
       </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>地盤が不等沈下することに起因。但し、地震による地盤の変化は“地震”に分類。</t>
+        </is>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" s="0" t="inlineStr">
+      <c r="A14" t="inlineStr">
         <is>
           <t>地域停電・法定停電</t>
         </is>
       </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>管理対象の施設の外部からの電力供給が停止したことに起因。</t>
+        </is>
+      </c>
     </row>
     <row r="15">
-      <c r="A15" s="0" t="inlineStr">
+      <c r="A15" t="inlineStr">
         <is>
           <t>給電不良</t>
         </is>
       </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>不具合を発生した設備への給電の異常。但し、地域停電・法定停電を除く。</t>
+        </is>
+      </c>
     </row>
     <row r="16">
-      <c r="A16" s="0" t="inlineStr">
+      <c r="A16" t="inlineStr">
         <is>
           <t>緑地の繁茂</t>
         </is>
       </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>対象物が緑地であるときに、手入れの不足などの要因により過剰な繁茂に至った。</t>
+        </is>
+      </c>
     </row>
     <row r="17">
-      <c r="A17" s="0" t="inlineStr">
+      <c r="A17" t="inlineStr">
         <is>
           <t>使用消耗</t>
         </is>
       </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>潤滑油の油量など、正常稼働により消耗が予定されている消耗。</t>
+        </is>
+      </c>
     </row>
     <row r="18">
-      <c r="A18" s="0" t="inlineStr">
+      <c r="A18" t="inlineStr">
         <is>
           <t>その他</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>これを選択した時には、具体的な部位は文で補足として追記する必要があります。</t>
         </is>
       </c>
     </row>
@@ -5084,72 +5623,117 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A9"/>
+  <dimension ref="A1:B9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="12"/>
   <cols>
     <col width="41.28515625" customWidth="1" style="9" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="0" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>汚れ・詰まり等の清掃</t>
         </is>
       </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>清掃等による原因除去。屋上などの排水溝の清掃なども含みます。</t>
+        </is>
+      </c>
     </row>
     <row r="2">
-      <c r="A2" s="0" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>取付不良・作動不良・ずれ等の調整</t>
         </is>
       </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>取付不良、作動不良、ずれ等の調整。</t>
+        </is>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="0" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>ボルト・ねじ等の増し締め</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>ボルト、ねじ等の増し締め直し。</t>
+        </is>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" s="0" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>潤滑用・グリス、充填油等の補充</t>
         </is>
       </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>潤滑用、グリス、充填油等の補充。</t>
+        </is>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" s="0" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>接触部分・回転部分等への注油</t>
         </is>
       </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>接触部分、回転部分等への注油。</t>
+        </is>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="0" t="inlineStr">
+      <c r="A6" t="inlineStr">
         <is>
           <t>軽微な損傷がある部分の補修</t>
         </is>
       </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>軽微な損傷がある部分の補修。</t>
+        </is>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="0" t="inlineStr">
+      <c r="A7" t="inlineStr">
         <is>
           <t>塗装</t>
         </is>
       </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>タッチペイント程度の軽微な塗装。</t>
+        </is>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" s="0" t="inlineStr">
+      <c r="A8" t="inlineStr">
         <is>
           <t>給排水設備に関連するパッキンの交換</t>
         </is>
       </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>給排水設備に関連するパッキンの交換。尚、パッキン以外も簡易な作業に含める場合もこの用語を利用してください。</t>
+        </is>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" s="0" t="inlineStr">
+      <c r="A9" t="inlineStr">
         <is>
           <t>その他軽微な作業</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>その他の包括施設管理事業者の負担で行う軽微な作業。</t>
         </is>
       </c>
     </row>
@@ -7166,114 +7750,189 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A15"/>
+  <dimension ref="A1:B15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="12"/>
   <cols>
     <col width="52.42578125" bestFit="1" customWidth="1" style="9" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="0" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>定期調査報告書</t>
         </is>
       </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>建築基準法施行規則の第三十六号の二様式</t>
+        </is>
+      </c>
     </row>
     <row r="2">
-      <c r="A2" s="0" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>定期調査報告概要書</t>
         </is>
       </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>建築基準法施行規則の第三十六号の三様式</t>
+        </is>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="0" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>定期検査報告書（建築設備（昇降機を除く））</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>建築基準法施行規則の第三十六号の六様式</t>
+        </is>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" s="0" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>定期検査報告概要書（建築設備（昇降機を除く））</t>
         </is>
       </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>建築基準法施行規則の第三十六号の七様式</t>
+        </is>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" s="0" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>定期検査報告書（防火設備）</t>
         </is>
       </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>建築基準法施行規則の第三十六号の八様式</t>
+        </is>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="0" t="inlineStr">
+      <c r="A6" t="inlineStr">
         <is>
           <t>定期検査報告概要書（防火設備）</t>
         </is>
       </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>建築基準法施行規則の第三十六号の九様式</t>
+        </is>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="0" t="inlineStr">
+      <c r="A7" t="inlineStr">
         <is>
           <t>防火対象物点検結果報告書</t>
         </is>
       </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>消防法施行規則（昭和三十六年自治省令第六号）第四条の二の四第三項の別記様式第一および第二</t>
+        </is>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" s="0" t="inlineStr">
+      <c r="A8" t="inlineStr">
         <is>
           <t>学校給食施設等定期検査票</t>
         </is>
       </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>学校給食衛生管理基準の「別紙3 定期及び日常の衛生検査の点検票」の第1票</t>
+        </is>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" s="0" t="inlineStr">
+      <c r="A9" t="inlineStr">
         <is>
           <t>学校給食設備等の衛生管理定期検査票</t>
         </is>
       </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>学校給食衛生管理基準の「別紙3 定期及び日常の衛生検査の点検票」の第2票</t>
+        </is>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" s="0" t="inlineStr">
+      <c r="A10" t="inlineStr">
         <is>
           <t>学校給食用食品の検収・保管等定期検査票</t>
         </is>
       </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>学校給食衛生管理基準の「別紙3 定期及び日常の衛生検査の点検票」の第3票</t>
+        </is>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" s="0" t="inlineStr">
+      <c r="A11" t="inlineStr">
         <is>
           <t>調理過程の定期検査票</t>
         </is>
       </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>学校給食衛生管理基準の「別紙3 定期及び日常の衛生検査の点検票」の第4票</t>
+        </is>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" s="0" t="inlineStr">
+      <c r="A12" t="inlineStr">
         <is>
           <t>学校給食従事者の衛生・健康状態定期検査票</t>
         </is>
       </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>学校給食衛生管理基準の「別紙3 定期及び日常の衛生検査の点検票」の第5票</t>
+        </is>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" s="0" t="inlineStr">
+      <c r="A13" t="inlineStr">
         <is>
           <t>定期検便結果処置票</t>
         </is>
       </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>学校給食衛生管理基準の「別紙3 定期及び日常の衛生検査の点検票」の第6票</t>
+        </is>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" s="0" t="inlineStr">
+      <c r="A14" t="inlineStr">
         <is>
           <t>学校給食における衛生管理体制定期検査票</t>
         </is>
       </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>学校給食衛生管理基準の「別紙3 定期及び日常の衛生検査の点検票」の第7票</t>
+        </is>
+      </c>
     </row>
     <row r="15">
-      <c r="A15" s="0" t="inlineStr">
+      <c r="A15" t="inlineStr">
         <is>
           <t>学校給食日常点検票</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>学校給食衛生管理基準の「別紙3 定期及び日常の衛生検査の点検票」の第8票</t>
         </is>
       </c>
     </row>
@@ -7288,37 +7947,71 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A4"/>
+  <dimension ref="A1:B4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="12"/>
   <cols>
     <col width="2.7109375" bestFit="1" customWidth="1" style="9" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="0" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>至急修繕・改修が必要。以下のいずれかに合致する
+・危険性: 施設使用者に危害を及ぼす可能性が非常に高い
+・利用への支障: 日常使用に著しい支障をもたらしている
+・法令適合性: 法令に不適合しており、且つ、非常時に施設の安全性が確保できない</t>
+        </is>
+      </c>
     </row>
     <row r="2">
-      <c r="A2" s="0" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>早急に修繕・改修が必要。以下のいずれかに合致する
+・危険性: 施設使用者に危害を及ぼす可能性がある
+・利用への支障: 施設利用者の日常使用に支障をもたらしている
+・法令適合性: 法令に不適合しており、且つ、非常時に施設の安全性が確保できない可能性がある</t>
+        </is>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="0" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>修繕・改修が必要。以下のいずれかに合致する
+・利用への支障: 施設利用者の日常利用に支障をきたしている
+・維持管理への悪影響: 早期に是正しなければ施設の寿命を縮める可能性がある
+・法令適合性: 法令に不適合しており、行政指導の対象となる</t>
+        </is>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" s="0" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>C</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>修繕・改修が望ましい。以下のいずれかに合致する
+・利用への支障: 施設利用者の日常使用に不便をもたらしている
+・その他: 美観・運用上、是正が望まれる
+・維持管理への悪影響: 放置すれば現在より修繕コストが高くなる可能性がある
+・法令適合性: 既存不適格（竣工時の法令には適していたが、現在の法令には適していない状態）
+　※既存不適格は改築・増築を行わなければ法令違反とはならない</t>
         </is>
       </c>
     </row>
@@ -7333,13 +8026,34 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:B2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="12"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="0" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>完了</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>以下の状況である事を示します。どの状況であっても、オーナーの承認が得られている必要があります。
+・修繕が完了し、修繕の完了をオーナーが承認された
+・不具合が見つからなかった。つまり、「案件(Complaint)」の「現象(phenomenon)」が“良好”である
+・修繕を行わない事が承認された
+・今後の作業や承認条件が決まらない事が承認された。例えば、完了条件や完了判断時期などが無い“経過観察”など</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>(その他)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>“完了”以外の文字列が登録されたときには、完了以前の状況である事を示します。つまり、何らかの作業や判断が残っている状況である事を示しています。</t>
         </is>
       </c>
     </row>
@@ -7354,20 +8068,48 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:B3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="12"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="0" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>発生</t>
         </is>
       </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>以下のステップの情報である事を示します。
+・不具合が発生した際の情報
+・不具合の発生時期が不明である場合は最初に不具合を認識した際の情報。例えば、最初の報告を行った時など</t>
+        </is>
+      </c>
     </row>
     <row r="2">
-      <c r="A2" s="0" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>完了</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>以下のステップである事を示します。どの状況であっても、オーナーの承認が得られている必要があります。
+・修繕が完了し、修繕の完了をオーナーが承認された
+・不具合が見つからなかった。つまり、「案件(Complaint)」の「現象(phenomenon)」が“良好”である
+・修繕を行わない事が承認された
+・今後の作業や承認条件が決まらない事が承認された。例えば、完了条件や完了判断時期などが無い“経過観察”など</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>(その他)</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>“発生”および“完了”以外の文字列が登録されたときには、“発生”から“完了”に至るまでの間のステップの情報である事を示しています。</t>
         </is>
       </c>
     </row>
@@ -7390,168 +8132,168 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="0" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>市区町村</t>
         </is>
       </c>
-      <c r="B1" s="0" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>地方公共団体の内の市町村、および特別区</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="0" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>都道府県</t>
         </is>
       </c>
-      <c r="B2" s="0" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>地方公共団体の内、都道府県</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="0" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>株式会社</t>
         </is>
       </c>
-      <c r="B3" s="0" t="inlineStr">
-        <is>
-          <t>会社法などの各種法令により規定されている法人の種類</t>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>会社法に基づく法人形態。出資者(株主)は出資額を限度とする有限責任を負い、株式の発行により資金調達を行う。日本で最も一般的な会社形態。</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="0" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>有限会社</t>
         </is>
       </c>
-      <c r="B4" s="0" t="inlineStr">
-        <is>
-          <t>会社法などの各種法令により規定されている法人の種類</t>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>旧有限会社法に基づき設立された法人形態。2006年の会社法施行により新設は廃止され、既存の有限会社は「特例有限会社」として存続している。出資者は有限責任を負う。</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="0" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>合名会社</t>
         </is>
       </c>
-      <c r="B5" s="0" t="inlineStr">
-        <is>
-          <t>会社法などの各種法令により規定されている法人の種類</t>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>会社法に基づく持分会社の一種。社員(出資者)全員が無限責任を負う。</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="0" t="inlineStr">
+      <c r="A6" t="inlineStr">
         <is>
           <t>合資会社</t>
         </is>
       </c>
-      <c r="B6" s="0" t="inlineStr">
-        <is>
-          <t>会社法などの各種法令により規定されている法人の種類</t>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>会社法に基づく持分会社の一種。無限責任を負う社員と有限責任を負う社員の両方で構成される。</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="0" t="inlineStr">
+      <c r="A7" t="inlineStr">
         <is>
           <t>合同会社</t>
         </is>
       </c>
-      <c r="B7" s="0" t="inlineStr">
-        <is>
-          <t>会社法などの各種法令により規定されている法人の種類</t>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>会社法に基づく持分会社の一種。社員全員が有限責任を負う。2006年の会社法施行により新設された、いわゆる日本版LLC。</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="0" t="inlineStr">
+      <c r="A8" t="inlineStr">
         <is>
           <t>国立研究開発法人</t>
         </is>
       </c>
-      <c r="B8" s="0" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>国立研究開発法人法で定められた法人</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="0" t="inlineStr">
+      <c r="A9" t="inlineStr">
         <is>
           <t>協同組合</t>
         </is>
       </c>
-      <c r="B9" s="0" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>中小企業等協同組合法など、各種法令で定められた協同組合</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="0" t="inlineStr">
+      <c r="A10" t="inlineStr">
         <is>
           <t>特定非営利活動法人</t>
         </is>
       </c>
-      <c r="B10" s="0" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>特定非営利活動促進法で定められた法人</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="0" t="inlineStr">
+      <c r="A11" t="inlineStr">
         <is>
           <t>地方共同法人</t>
         </is>
       </c>
-      <c r="B11" s="0" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>地方共同法人法で定められた法人</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="0" t="inlineStr">
+      <c r="A12" t="inlineStr">
         <is>
           <t>独立行政法人</t>
         </is>
       </c>
-      <c r="B12" s="0" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>独立行政法人通則法で定められた法人</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="0" t="inlineStr">
+      <c r="A13" t="inlineStr">
         <is>
           <t>一般社団法人</t>
         </is>
       </c>
-      <c r="B13" s="0" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>一般社団法人及び一般財団法人に関する法律で定められた法人</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="0" t="inlineStr">
+      <c r="A14" t="inlineStr">
         <is>
           <t>一般財団法人</t>
         </is>
       </c>
-      <c r="B14" s="0" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>一般社団法人及び一般財団法人に関する法律で定められた法人</t>
         </is>
@@ -7568,308 +8310,230 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A43"/>
+  <dimension ref="A1:A30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="12"/>
   <cols>
     <col width="34.42578125" bestFit="1" customWidth="1" style="9" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="0" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>一戸建ての住宅</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="0" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>長屋</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="0" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>共同住宅</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="0" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>幼稚園</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="0" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>小学校</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="0" t="inlineStr">
+      <c r="A6" t="inlineStr">
         <is>
           <t>義務教育学校</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="0" t="inlineStr">
-        <is>
-          <t>中学校</t>
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>中学校
+高等学校
+中等教育学校</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="0" t="inlineStr">
-        <is>
-          <t>高等学校</t>
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>特別支援学校</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="0" t="inlineStr">
-        <is>
-          <t>中等教育学校</t>
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>大学
+高等専門学校</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="0" t="inlineStr">
-        <is>
-          <t>特別支援学校</t>
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>専修学校</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="0" t="inlineStr">
-        <is>
-          <t>大学</t>
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>各種学校</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="0" t="inlineStr">
-        <is>
-          <t>高等専門学校</t>
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>幼保連携型認定こども園</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="0" t="inlineStr">
-        <is>
-          <t>専修学校</t>
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>図書館</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="0" t="inlineStr">
-        <is>
-          <t>各種学校</t>
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>博物館</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="0" t="inlineStr">
-        <is>
-          <t>幼保連携型認定こども園</t>
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>美術館</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="0" t="inlineStr">
-        <is>
-          <t>図書館</t>
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>老人ホーム
+福祉ホーム</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="0" t="inlineStr">
-        <is>
-          <t>博物館</t>
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>保育所</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="0" t="inlineStr">
-        <is>
-          <t>美術館</t>
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>助産所</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="0" t="inlineStr">
-        <is>
-          <t>老人ホーム</t>
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>児童福祉施設</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="0" t="inlineStr">
-        <is>
-          <t>福祉ホーム</t>
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>診療所</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="0" t="inlineStr">
-        <is>
-          <t>保育所</t>
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>病院</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="0" t="inlineStr">
-        <is>
-          <t>助産所</t>
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>巡査派出所</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="0" t="inlineStr">
-        <is>
-          <t>児童福祉施設</t>
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>税務署
+警察署
+保健所
+消防署</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="0" t="inlineStr">
-        <is>
-          <t>診療所</t>
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>工場（自動車修理工場を除く。）</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="0" t="inlineStr">
-        <is>
-          <t>病院</t>
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>ボーリング場
+スケート場
+水泳場
+スキー場
+ゴルフ練習場
+バッティング練習場</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="0" t="inlineStr">
-        <is>
-          <t>巡査派出所</t>
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>体育館
+スポーツの練習場</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="0" t="inlineStr">
-        <is>
-          <t>税務署</t>
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>自動車車庫</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="0" t="inlineStr">
-        <is>
-          <t>警察署</t>
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>自転車駐車場</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="0" t="inlineStr">
-        <is>
-          <t>保健所</t>
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>公会堂又は集会場</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="0" t="inlineStr">
-        <is>
-          <t>消防署</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="0" t="inlineStr">
-        <is>
-          <t>工場（自動車修理工場を除く。）</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="0" t="inlineStr">
-        <is>
-          <t>ボーリング場</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="0" t="inlineStr">
-        <is>
-          <t>スケート場</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="0" t="inlineStr">
-        <is>
-          <t>水泳場</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="0" t="inlineStr">
-        <is>
-          <t>スキー場</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="0" t="inlineStr">
-        <is>
-          <t>ゴルフ練習場</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="0" t="inlineStr">
-        <is>
-          <t>バッティング練習場</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="0" t="inlineStr">
-        <is>
-          <t>体育館</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="0" t="inlineStr">
-        <is>
-          <t>スポーツの練習場</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="0" t="inlineStr">
-        <is>
-          <t>自動車車庫</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="0" t="inlineStr">
-        <is>
-          <t>自転車駐車場</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="0" t="inlineStr">
-        <is>
-          <t>公会堂又は集会場</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="0" t="inlineStr">
+      <c r="A30" t="inlineStr">
         <is>
           <t>卸売市場</t>
         </is>
@@ -7894,126 +8558,126 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="0" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>業務施設</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="0" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>商業施設</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="0" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>宿泊施設</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="0" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>商業系用途複合施設</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="0" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>住宅</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="0" t="inlineStr">
+      <c r="A6" t="inlineStr">
         <is>
           <t>共同住宅</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="0" t="inlineStr">
+      <c r="A7" t="inlineStr">
         <is>
           <t>店舗等併用住宅</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="0" t="inlineStr">
+      <c r="A8" t="inlineStr">
         <is>
           <t>店舗等併用共同住宅</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="0" t="inlineStr">
+      <c r="A9" t="inlineStr">
         <is>
           <t>作業所併用住宅</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="0" t="inlineStr">
+      <c r="A10" t="inlineStr">
         <is>
           <t>官公庁施設</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="0" t="inlineStr">
+      <c r="A11" t="inlineStr">
         <is>
           <t>文教厚生施設</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="0" t="inlineStr">
+      <c r="A12" t="inlineStr">
         <is>
           <t>運輸倉庫施設</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="0" t="inlineStr">
+      <c r="A13" t="inlineStr">
         <is>
           <t>工場</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="0" t="inlineStr">
+      <c r="A14" t="inlineStr">
         <is>
           <t>農林漁業用施設</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="0" t="inlineStr">
+      <c r="A15" t="inlineStr">
         <is>
           <t>供給処理施設</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="0" t="inlineStr">
+      <c r="A16" t="inlineStr">
         <is>
           <t>防衛施設</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="0" t="inlineStr">
+      <c r="A17" t="inlineStr">
         <is>
           <t>その他</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="0" t="inlineStr">
+      <c r="A18" t="inlineStr">
         <is>
           <t>不明</t>
         </is>
@@ -8639,91 +9303,91 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="0" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>第一種低層住居専用地域</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="0" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>第二種低層住居専用地域</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="0" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>第一種中高層住居専用地域</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="0" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>第二種中高層住居専用地域</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="0" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>第一種住居地域</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="0" t="inlineStr">
+      <c r="A6" t="inlineStr">
         <is>
           <t>第二種住居地域</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="0" t="inlineStr">
+      <c r="A7" t="inlineStr">
         <is>
           <t>準住居地域</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="0" t="inlineStr">
+      <c r="A8" t="inlineStr">
         <is>
           <t>田園住居地域</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="0" t="inlineStr">
+      <c r="A9" t="inlineStr">
         <is>
           <t>近隣商業地域</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="0" t="inlineStr">
+      <c r="A10" t="inlineStr">
         <is>
           <t>商業地域</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="0" t="inlineStr">
+      <c r="A11" t="inlineStr">
         <is>
           <t>準工業地域</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="0" t="inlineStr">
+      <c r="A12" t="inlineStr">
         <is>
           <t>工業地域</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="0" t="inlineStr">
+      <c r="A13" t="inlineStr">
         <is>
           <t>工業専用地域</t>
         </is>
@@ -8740,44 +9404,69 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:B5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="12"/>
   <cols>
     <col width="41.28515625" customWidth="1" style="9" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="0" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>不具合連絡</t>
         </is>
       </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>施設や設備に不具合があったときに連絡する連絡先です</t>
+        </is>
+      </c>
     </row>
     <row r="2">
-      <c r="A2" s="0" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>予約</t>
         </is>
       </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>予約、予約の変更、予約の確認など、予約に関する連絡先です</t>
+        </is>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="0" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>警備</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>警備関連の連絡先です</t>
+        </is>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" s="0" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>総合</t>
         </is>
       </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>総合窓口の連絡先です。代表電話を含みます</t>
+        </is>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" s="0" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>その他</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>その他の連絡先です</t>
         </is>
       </c>
     </row>
@@ -8799,343 +9488,343 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="0" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>大気汚染</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="0" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>大気圧</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="0" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>平均速度</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="0" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>バッテリ寿命</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="0" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>バッテリ供給</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="0" t="inlineStr">
+      <c r="A6" t="inlineStr">
         <is>
           <t>CDOM（着色溶存有機物）</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="0" t="inlineStr">
+      <c r="A7" t="inlineStr">
         <is>
           <t>コンダクタンス</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="0" t="inlineStr">
+      <c r="A8" t="inlineStr">
         <is>
           <t>電気伝導率</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="0" t="inlineStr">
+      <c r="A9" t="inlineStr">
         <is>
           <t>深さ</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="0" t="inlineStr">
+      <c r="A10" t="inlineStr">
         <is>
           <t>摂食活動</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="0" t="inlineStr">
+      <c r="A11" t="inlineStr">
         <is>
           <t>電力消費量</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="0" t="inlineStr">
+      <c r="A12" t="inlineStr">
         <is>
           <t>エネルギー</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="0" t="inlineStr">
+      <c r="A13" t="inlineStr">
         <is>
           <t>充填率</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="0" t="inlineStr">
+      <c r="A14" t="inlineStr">
         <is>
           <t>遊離塩素</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="0" t="inlineStr">
+      <c r="A15" t="inlineStr">
         <is>
           <t>ガス消費量</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="0" t="inlineStr">
+      <c r="A16" t="inlineStr">
         <is>
           <t>ゲート開閉</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="0" t="inlineStr">
+      <c r="A17" t="inlineStr">
         <is>
           <t>方位</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="0" t="inlineStr">
+      <c r="A18" t="inlineStr">
         <is>
           <t>湿度</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="0" t="inlineStr">
+      <c r="A19" t="inlineStr">
         <is>
           <t>光</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="0" t="inlineStr">
+      <c r="A20" t="inlineStr">
         <is>
           <t>位置</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="0" t="inlineStr">
+      <c r="A21" t="inlineStr">
         <is>
           <t>搾乳</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="0" t="inlineStr">
+      <c r="A22" t="inlineStr">
         <is>
           <t>動作</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="0" t="inlineStr">
+      <c r="A23" t="inlineStr">
         <is>
           <t>移動</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="0" t="inlineStr">
+      <c r="A24" t="inlineStr">
         <is>
           <t>騒音レベル</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="0" t="inlineStr">
+      <c r="A25" t="inlineStr">
         <is>
           <t>占有率</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="0" t="inlineStr">
+      <c r="A26" t="inlineStr">
         <is>
           <t>酸化還元電位（ORP）</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="0" t="inlineStr">
+      <c r="A27" t="inlineStr">
         <is>
           <t>pH</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="0" t="inlineStr">
+      <c r="A28" t="inlineStr">
         <is>
           <t>電力</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="0" t="inlineStr">
+      <c r="A29" t="inlineStr">
         <is>
           <t>降水量</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="0" t="inlineStr">
+      <c r="A30" t="inlineStr">
         <is>
           <t>圧力</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="0" t="inlineStr">
+      <c r="A31" t="inlineStr">
         <is>
           <t>屈折率</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="0" t="inlineStr">
+      <c r="A32" t="inlineStr">
         <is>
           <t>塩分濃度</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="0" t="inlineStr">
+      <c r="A33" t="inlineStr">
         <is>
           <t>煙</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="0" t="inlineStr">
+      <c r="A34" t="inlineStr">
         <is>
           <t>土壌湿度</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="0" t="inlineStr">
+      <c r="A35" t="inlineStr">
         <is>
           <t>日射量</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="0" t="inlineStr">
+      <c r="A36" t="inlineStr">
         <is>
           <t>速度</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="0" t="inlineStr">
+      <c r="A37" t="inlineStr">
         <is>
           <t>総溶解固形物濃度（TDS）</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="0" t="inlineStr">
+      <c r="A38" t="inlineStr">
         <is>
           <t>温度</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="0" t="inlineStr">
+      <c r="A39" t="inlineStr">
         <is>
           <t>交通量</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="0" t="inlineStr">
+      <c r="A40" t="inlineStr">
         <is>
           <t>浮遊物質量（TSS）</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="0" t="inlineStr">
+      <c r="A41" t="inlineStr">
         <is>
           <t>濁度</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="0" t="inlineStr">
+      <c r="A42" t="inlineStr">
         <is>
           <t>水消費量</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="0" t="inlineStr">
+      <c r="A43" t="inlineStr">
         <is>
           <t>水流量</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="0" t="inlineStr">
+      <c r="A44" t="inlineStr">
         <is>
           <t>水位</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="0" t="inlineStr">
+      <c r="A45" t="inlineStr">
         <is>
           <t>水質汚染</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="0" t="inlineStr">
+      <c r="A46" t="inlineStr">
         <is>
           <t>天候状況</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="0" t="inlineStr">
+      <c r="A47" t="inlineStr">
         <is>
           <t>重量</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="0" t="inlineStr">
+      <c r="A48" t="inlineStr">
         <is>
           <t>風向</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="0" t="inlineStr">
+      <c r="A49" t="inlineStr">
         <is>
           <t>風速</t>
         </is>
@@ -9152,30 +9841,33 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:B2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="12"/>
   <cols>
     <col width="14.140625" bestFit="1" customWidth="1" style="9" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="0" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>法人番号</t>
         </is>
       </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>法人番号であることを示します。対となるID(identification)には、数字からなる13桁のASCII文字列([GIF](https://ppp-database.org/howtouse/terms-g/#gif)の半角と同義)で格納します。</t>
+        </is>
+      </c>
     </row>
     <row r="2">
-      <c r="A2" s="0" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>自治体コード</t>
         </is>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="0" t="inlineStr">
-        <is>
-          <t>不動産ID</t>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>全国地方公共団体コード(自治体コード)であることを示します。対となるID(identification)には、数字からなる6桁のASCII文字列(半角文字)で格納します。</t>
         </is>
       </c>
     </row>
